--- a/questions.xlsx
+++ b/questions.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -27,158 +27,98 @@
     <t>Question</t>
   </si>
   <si>
-    <t>Вопрос 1:  В подобных случаях китайцы говорят о птичьем, немцы — об испанском, англичане — о греческом, а турки — о французском. Назовите фразеологизмом из двух слов ту, о которой вспоминают русские.
-Ответ: Китайская грамота.
-Комментарий: Когда немцы не понимают чего-то, они говорят, что это для них испанский язык. Англичане говорят: "It's Greek to me". Китайцы говорят про птичий язык. Надеемся, что наш турнир не станет для вас "китайской грамотой". Желаем удачи всем играющим командам!</t>
-  </si>
-  <si>
-    <t>Вопрос 18: Перед саммитом Шанхайской организации сотрудничества владельцев магазинов в центре Екатеринбурга обязали произвести два аналогичных мероприятия. Первое особых проблем не вызвало: многие торговцы даже могли провести его самостоятельно. А вот со вторым были сложности — даже просто проверить его исполнение торговцам было трудно, ибо они в массе своей не знали ЭТОГО. Назовите ЭТО, ставшее в русском языке идиомой.
-Ответ: Китайская грамота.
-Комментарий: От торговцев потребовали завести ценники на английском и китайском. Английский текст многим торговцам оказался вполне по зубам, а вот китайская грамота — она и есть китайская грамота. Поди разберись, что там понаписали иероглифами...</t>
-  </si>
-  <si>
-    <t>Вопрос 34: Не побоявшись общественного гнева, юморист Барри Хамфрис заявил, что, в отличие от НЕЁ, умеет плавать. Все события произведения, в названии которого фигурирует ОНА, происходят в одной комнате. Назовите ЕЁ.
-Ответ: Вирджиния Вулф.
-Зачёт: по фамилии Вулф или Вульф без неверных уточнений.
-Комментарий: в 1941 году Вирджиния Вулф покончила жизнь самоубийством, утопившись в реке. Барри Хамфрис не побоялся шутить на эту чёрную тему. Действие пьесы Эдварда Олби «Кто боится Вирджинии Вулф?» происходит в одной гостиной. Слово «комната» могло напомнить вам об эссе Вирджинии Вулф «Своя комната».</t>
-  </si>
-  <si>
-    <t>Вопрос 4: Рассказывают, что в 1928 году перед парижской премьерой фильма "Андалузский пес" Луис Бунюэль наполнил [ПРОПУСК] на случай возможного скандала. 28 марта 1941 года Вирджиния Вулф оставила письмо мужу и наполнила [ПРОПУСК]. Заполните любой из пропусков двумя словами, начинающимися с одной и той же буквы.
-Ответ: "... карманы камнями...".
-Зачёт: "... камнями карманы...".
-Комментарий: Бунюэль сделал это, чтобы в случае скандала иметь возможность отбиться от разъяренных зрителей (но опасения режиссера оказались напрасными). Будучи в глубокой депрессии, Вулф написала прощальное письмо, наполнила карманы камнями и утопилась в реке.</t>
-  </si>
-  <si>
-    <t>Вопрос 42: В 90-е хоккейный «Детройт» был одним из сильнейших клубов НХЛ. Комментируя невзрачную игру нынешнего «Детройта», комментаторы Eurosport вспомнили строку из произведения 1995 года. Назовите любого из его авторов.
-Ответ: Илья Кормильцев.
-Зачёт: Вячеслав Бутусов, Кормильцев, Бутусов.
-Комментарий: «Где твои крылья, которые нравились мне». Кормильцев написал слова для песни, Бутусов музыку. Полное название команды — «Детройт Ред Уингз»</t>
-  </si>
-  <si>
-    <t>Вопрос 14: Компания "Quiksilver" [квиксИльвер] производит экипировку для серфингистов и сноубордистов. Чтобы символично обозначить оба вида спорта, дизайнеры разработали логотип, взяв за основу произведение XIX века. Назовите его автора.
-https://db.chgk.info/images/db/20150829.jpg
-Ответ: Хокусай.
-Комментарий: На сёрфинг намекает изображение волны, а на сноубординг — изображение горы. Упомянутое произведение — гравюра Хокусая "Большая волна в Канагаве" из цикла "Тридцать шесть видов Фудзи".</t>
-  </si>
-  <si>
-    <t>Вопрос 8: По словам Брайана Грина, Ньютон объявил, что абсолютно всё оказывает воздействие на абсолютно всё во Вселенной. Грин пишет, что ньютоновскую концепцию тяготения можно было бы назвать так же, как называют американца, жившего в девятнадцатом веке. Назовите этого американца.
-Ответ: [Сэмюэль] Кольт.
-Комментарий: Поскольку все объекты во Вселенной оказывают и испытывают воздействие тяжести, получается определенное равенство, поэтому теория Ньютона — своеобразный великий уравнитель.</t>
-  </si>
-  <si>
-    <t>Вопрос 9: В фильме "Седьмая печать" актер, рассматривающий маску смерти, говорит, что скоро он выступит ТАМ. В другом произведении актеры исполнили ТАМ пьесу "Убийство Гонзаго". Ответьте как можно точнее: где именно?
-Ответ: В Эльсиноре.
-Комментарий: Маска смерти напоминает череп. Гамлет из одноименного произведения Шекспира попросил приехавших актеров исполнить пьесу "Убийство Гонзаго", вставив туда несколько строк собственного сочинения.</t>
-  </si>
-  <si>
-    <t>Вопрос 8:
-https://db.chgk.info/images/db/20150555.jpg
-    На фотографии — один из сувениров, которые можно приобрести в музейной лавке. Назовите город, в котором находится эта лавка.
-Ответ: Хельсингёр.
-Зачёт: Эльсинор; Гельсинор.
-Комментарий: Город, в котором происходит действие "Гамлета"; в музейной лавке можно приобрести, в частности, "череп Йорика", книги Шекспира и о Шекспире (на фотографии можно их разглядеть).</t>
-  </si>
-  <si>
-    <t>Вопрос 46:
-https://db.chgk.info/images/db/20100829.jpg
-    Данное фото сделано в Ампурдане, поэтому на нем вряд ли изображен ИКС. Тем не менее, того, кто причастен к появлению "ИКСА", вы видите, хотя его и трудно узнать. Назовите ИКСА двумя словами.
-Ответ: Андалузский пес.
-Комментарий: На фото изображен пятилетний Сальвадор Дали, которого без усов узнать многим весьма трудно. Рядом с ним его собака, но так как фото сделано в Ампурдане — одной из частей Каталонии, то пес явно не андалузский.</t>
-  </si>
-  <si>
-    <t>Вопрос 11: Эвита Перон считала поэтессу Викторию Окампо безнадежно глупой. Ответьте максимально точно, с кем, обыгрывая имя поэтессы, сравнивала ее Перон.
-Ответ: С Никой Самофракийской.
-Комментарий: Тоже победа, и тоже безголовая…</t>
-  </si>
-  <si>
-    <t>Вопрос 22:
-Раздаточный материал
-    katya2@imperatrica.com — Екатерина II
-    kurbsky@anti-ivan.lt — кн. Андрей Курбский
-    ioannpii@vatikan.org — Кароль Войтыла
-    etat@france.fr
-    Перед вами вымышленные почтовые адреса известных личностей. Назовите абсолютно точно человека, которому приписан адрес etat@france.fr.
-Ответ: Людовик XIV.
-Зачёт: Король-Солнце. Незачет: Людовик.
-Комментарий: Людовику XIV приписывают фразу "Государство — это я".</t>
-  </si>
-  <si>
-    <t>Вопрос 7: "В 1982 году на русском грузовом судне, ставшем на якорь у побережья Сассекса, на мостике была замечена сутулая фигура с биноклем в руках". Имя, под которым стал известен этот человек, совпадает с фамилией главы государства. Какого государства?
-Ответ: КНДР.
-Зачёт: Северная Корея.
-Комментарий: Это был знаменитый разведчик Ким Филби, решивший в последний раз взглянуть на родину. Разумеется, въезд в Великобританию ему был запрещен.
-    Примечание: Ким — это псевдоним.</t>
-  </si>
-  <si>
-    <t>Вопрос 5: По мнению Кима, с таким сосредоточенным и напряженным лицом Максим бы и дня не продержался. Назовите фамилии обоих.
-Ответ: Филби, Исаев.
-Зачёт: Филби, Штирлиц.
-Комментарий: Известный советский шпион Ким Филби заявил после просмотра кинофильма "Семнадцать мгновений весны": "С таким сосредоточенным и напряженным лицом настоящий Штирлиц не продержался бы и дня!".</t>
-  </si>
-  <si>
-    <t>Вопрос 4: Герой ЖоЭля ДиккЕра вспоминает, что незадолго до казни супругов РОзенберг на Бродвее впервые поставили пьесу, персонажами которой являются в том числе Абигайль Уильямс и Ребекка Нёрс. В каком городе происходит действие этой пьесы?
-Ответ: Салем.
-Зачёт: Сейлем.
-Комментарий: Это пьеса Артура Миллера "Салемские колдуньи" (оригинальное название пьесы — "Суровое испытание"). Довольно очевидна параллель между пуританской охотой на ведьм и маккартистскими чистками и шпиономанией. У пуритан часто встречались библейские имена. Пьеса Миллера была поставлена в январе 1953 года, а Розенбергов казнили в июне того же года.</t>
-  </si>
-  <si>
-    <t>Вопрос 75: В одном сериале герой проникается презрением к коллекционеру, собирающему картины Гитлера. Однако герой меняет своё мнение, когда, войдя в зал с картинами, понимает, что находится в своеобразном ИКСЕ. Назовите ИКС словом латинского происхождения.
-Ответ: колумбарий.
-Комментарий: коллекционер не был поклонником Гитлера, а как раз наоборот — он приобретал картины, чтобы сжечь их. Зал с картинами оказался колумбарием, а на каждой вазе с «прахом» было подписано, какая это была картина.</t>
-  </si>
-  <si>
-    <t>Вопрос 2: В сатирическом эссе Остин Холиок высказывал сомнение в том, что свой ОН есть в недрах каждой населённой планеты. Следовательно, многих людей ждёт знакомство с инопланетянами. Какое определение дал ЕМУ автор произведения середины XX века?
-Ответ: [ад —] это другие.
-Зачёт: по слову «другие».
-Комментарий: Остин Холиок написал сатирическое эссе на тему природы и местонахождения рая и ада. Холиок размышлял, куда после смерти попадают инопланетяне. Так, он писал, что поскольку вряд ли в недрах каждой населённой планеты есть свой локальный адок, все грешные существа должны попадать в один общий ад, а значит, многих людей ждёт знакомство с инопланетянами. Утверждение «ад — это другие» Сартр сформулировал в своей пьесе «За закрытыми дверями».</t>
-  </si>
-  <si>
-    <t>Вопрос 6: Брайс Девитт цитирует это произведение во введении книги "Многомировая интерпретация квантовой механики". В оригинальном названии этого произведения есть слово, однокоренное слову "бифуркация". Назовите это произведение.
-Ответ: "Сад расходящихся тропок".
-Комментарий: Многомировая интерпретация квантовой механики описывает множество альтернативных Вселенных, в которых реализуются все возможные варианты развития событий. В рассказе Борхеса "Сад расходящихся тропок" можно увидеть множественные параллели с этой идеей. Бифуркация — это разветвление. По-испански произведение называется "El Jardín de senderos que se bifurcan".</t>
-  </si>
-  <si>
-    <t>Вопрос 46: В начале XX [двадцатого] века Сергей АльпЕров в своих номерах высмеивал самодержавие, а после революции выступал перед бойцами Красной армии. Как ни странно, в дуэте с Борисом МухнИцким АльпЕров был ИМ. Назовите ЕГО двумя словами.
-Ответ: белый клоун.
-Комментарий: в парной цирковой буффонаде есть 2 типажа: белый клоун, который отличается высокомерием, умом и злопамятностью, и легкомысленный, простоватый рыжий клоун. Альперов в дуэте исполнял роль белого клоуна, хотя сам симпатий к белым не питал и даже занимался национализацией цирков при советской власти.</t>
-  </si>
-  <si>
-    <t>Вопрос 2: О НЕЙ и мудреце написана опера. Герой детской книги, став ЕЮ, почувствовал, что у него в животе дух захватывает. Назовите ЕЕ.
+    <t>Вопрос 4:
+https://db.chgk.info/images/db/20121062.jpg
+    Сначала мы желали спрятать на раздаточном материале больше, но скрытая от вас заглавная "героиня" вырвала гвозди, которыми была прибита. Назовите эту "героиню".
+Ответ: Шагреневая кожа.
+Комментарий: После выполнения желаний шагреневая кожа уменьшалась в размерах, и ничто не могло остановить процесс сокращения.</t>
+  </si>
+  <si>
+    <t>Вопрос 9: "Побережем осла, если хотим дожить до старости!". Из какого романа XIX века взята эта образная ремарка автора?
+Ответ: "Шагреневая кожа".
+Комментарий: Шагреневая кожа была выделанной особым образом ослиной шкурой. Как известно, она сжималась при каждом выполненном желании владельца, сокращая его жизнь.</t>
+  </si>
+  <si>
+    <t>Вопрос 3: Основная черта гипертекста — нелинейность повествования. Энрике Шмидт, рассуждая о будущем литературных гипертекстов, задается вопросом: "Цветут ли ИКСЫ?". Назовите ИКС тремя словами.
+Ответ: Сад расходящихся тропок.
+Комментарий: "Сад расходящихся тропок" — рассказ Борхеса, представляющий собой классический пример литературного гипертекста.</t>
+  </si>
+  <si>
+    <t>Вопрос 28: Кому посвящён объект площадью более шести тысяч квадратных метров, созданный основателем компании «Минотавр Дизайн» в южноамериканском городе Сан-Рафаэ́ль?
+Ответ: [Хо́рхе Луи́су] Бо́рхесу.
+Зачёт: по фамилии.
+Комментарий: в аргентинском городе Сан-Рафаэль находится «Лабиринт Борхеса», в котором есть множество расходящихся тропок. «Сад расходящихся тропок» – знаменитый рассказ Хорхе Луиса Борхеса.</t>
+  </si>
+  <si>
+    <t>Вопрос 3: Дуплет.
+    1. Евгения Гинзбург пишет, что для девушки, выросшей в Харбине и вернувшейся позже в Советский союз, "потери бдительности", "примиренчество" и "гнилые либерализмы" звучали ЭТИМ. Назовите ЭТО.
+    2. Крупнейший в истории проект, призванный защитить северные районы одной страны от нашествия пустыни, называется "Зеленая ОНА". Назовите ЕЕ двумя словами.
+Ответ:
+    1. Китайская грамота.
+    2. Китайская стена.
+Комментарий:
+    1. Девушка работала на Китайской Восточной железной дороге и вернулась в СССР после продажи дороги Китаю.
+    2. По аналогии с Великой китайской стеной, которая должна была защитить север Китая от нашествия кочевников.</t>
+  </si>
+  <si>
+    <t>Вопрос 12: Вину на себя взял француз Робер Юбер, из-за чего многие заподозрили заговор папистов. И лишь много позже официально был признан факт нарушения техники безопасности. А в чем обвиняли Юбера?
+Ответ: В Великом лондонском пожаре.
+Зачёт: В Большом лондонском пожаре; в лондонском пожаре 1666 года.
+Комментарий: Как и большинство пожаров, тот возник из-за неосторожного обращения с огнем (в пекарне), а Юбер был просто одержим манией величия.</t>
+  </si>
+  <si>
+    <t>Вопрос 2: В статье о НЕЙ в качестве "первопроходцев" названы наркомы Александра Коллонтай и Павел Дыбенко. Другую ЕЕ планировалось описать еще в первой книге. Назовите ЕЕ двумя словами.
+Ответ: Красная свадьба.
+Комментарий: В противовес церковному венчанию в 1920-х годах стали практиковаться т.н. "красные свадьбы". Во втором случае речь идет о событиях эпопеи Джорджа Р.Р. Мартина.</t>
+  </si>
+  <si>
+    <t>Вопрос 5: Персонаж одного фэнтезийного рассказа пришел в гости к женщине, но увидел на пороге дома дракона. Через некоторое время, в то время как персонаж пил с женщиной чай, его начал мучить вопрос. Назовите любого из тех, кто фигурирует в похожем вопросе, возникшем до нашей эры.
 Ответ: Бабочка.
-Комментарий: Герой сказки Валерия Медведева превратился в бабочку и во время полета всё время проваливался в воздушные ямы. Слова "в животе" могли послужить подсказкой. Сложные взаимоотношения с чешуекрылыми были у философа Чжуан-цзы, который так и не смог понять, снилось ли ему, что он стал бабочкой, или бабочке снилось, что она стала философом. Современная китайская опера так и называется — "Сон Чжуан-цзы о бабочке".</t>
-  </si>
-  <si>
-    <t>Вопрос 7: По легенде, когда ОН однажды нагИм проходил мимо тОржища, женщины стали насмехаться над НИМ и тут же ослепли. Правда, к торговкам в итоге зрение всё же вернулось. Назовите ЕГО.
-Ответ: Василий Блаженный.
-Зачёт: Блаженный Василий.
-Комментарий: Василий, как и полагает блаженному, отличался эксцентричным внешним видом и поведением. Согласно апОкрифу, оскорбившие его женщины ослепли, однако тут же покаялись и исцелились. Более известна другая легенда, согласно которой Иван Грозный ослепил Барму и Постника, архитекторов Собора Василия Блаженного.</t>
-  </si>
-  <si>
-    <t>Вопрос 6: Арка Константина в Риме составлена из большого количества фрагментов разных стилей. В итальянском прозвище арки фигурирует ОНА. ОНА — заглавная героиня итальянского произведения XIX века. Что это за произведение?
-Ответ: "Сорока-воровка".
-Комментарий: Фрагменты арки натасканы из разных стилей, как добыча сороки. В опере Россини "Сорока-воровка" важную роль играет настоящая сорока.</t>
-  </si>
-  <si>
-    <t>Вопрос 4: В статье Википедии "Скороговорка" упоминается слово, пришедшее из языка афразийской макросемьи. Напишите его.
-Ответ: Шибболет.
-Комментарий: Как известно, тех, кто не мог выговорить слово "шибболет" правильно, ждала незавидная участь. Аналогичным способом для распознания "свой-чужой" можно использовать и скороговорки. Слово "шибболет" пришло из иврита, который относится к афразийской языковой макросемье.</t>
-  </si>
-  <si>
-    <t>Вопрос 13: По словам Юрия Дрозда, в этом городе был сухой климат, и поэтому поступок людей, наполнивших бочки, тоже можно считать чудом. Назовите этот город.
+Зачёт: Чжуан-цзы.
+Комментарий: Дракон превращается в женщину, и героя начинает мучить вопрос, кто же перед ним — женщина, которая умеет превращаться в дракона, или дракон, умеющий превращаться в женщину. Легенда гласит, что однажды философ Чжуан-цзы заснул, и ему приснилось, что он бабочка, которой снится, что она Чжуан-цзы. Проснувшись, философ долго не мог понять, кто же он на самом деле — Чжуан-цзы или бабочка.</t>
+  </si>
+  <si>
+    <t>Вопрос 1: В романе НатАниэля ГОторна "Алая буква" осуждается пуританское общество Новой Англии. Еще в молодости Готорн несколько изменил фамилию, полученную при рождении, чтобы скрыть родство с одним из предков, который председательствовал... Ответьте абсолютно точно, где именно.
+Ответ: На суде над салемскими ведьмами.
+Комментарий: При рождении Готорн получил фамилию Гаторн, но отвращение к предку побудило ее изменить (добавить "w"). Салемский процесс — пример религиозного мракобесия пуритан Новой Англии.</t>
+  </si>
+  <si>
+    <t>Вопрос 4: Рекламу компании "Nike", в которой ОН называет себя патроном в обойме, затем пришлось срочно снять с эфира. Назовите ЕГО.
+Ответ: [Оскар] ПистОриус.
+Комментарий: Знаменитый южноафриканский спортсмен застрелил свою девушку, в результате клип стал выглядеть несколько странно.</t>
+  </si>
+  <si>
+    <t>Вопрос 7: В фильме "Перси Джексон и Море чудовищ" показано, как Зевс неким образом наказал Диониса. Назовите топоним, известный благодаря случаю, обратному этому наказанию.
 Ответ: Кана [Галилейская].
-Комментарий: В Кане Галилейской свое первое чудо сотворил Иисус Христос, когда превратил воду в вино. Оказывается, наполнить бочки водой было тоже непросто.</t>
-  </si>
-  <si>
-    <t>Вопрос 4:
-https://db.chgk.info/images/db/20160119.jpg
-    В сериале "Доктор Кто" помогающих Великобритании дАлеков Уинстон Черчилль называет ИМИ, подразумевая стойкость и дисциплину. Назовите ИХ словом с двумя корнями.
-Ответ: Железнобокие.
-Комментарий: Черчилль дает прозвище дАлекам в честь кавалерии Оливера Кромвеля. Для закованных в металлическую конструкцию дАлеков оно подходит буквально.</t>
-  </si>
-  <si>
-    <t>Вопрос 3: РататОск в скандинавской мифологии — белка, бегающая по мировому древу. Музыкант, взявший псевдоним Рататоск, в дебютном альбоме использовал ЕЕ. ОНА выпускается, в том числе, под маркой "Stradivarius" [страдивАриус]. Назовите ЕЕ.
-Ответ: [Музыкальная] пила.
-Комментарий: Пила, как и белка, имеет отношение к дереву, хотя в скандинавских мифах ясень Иггдрасиль грызет дракон Нидхёгг, а не Рататоск. На музыкальной пиле играют смычком, отсюда брэнд "Stradivarius".</t>
+Комментарий: У наказанного Диониса вино превращалось в воду. В Кане Галилейской Иисус превращал воду в вино.</t>
+  </si>
+  <si>
+    <t>Вопрос 13: Жизнь Вирджинии Вульф окончилась трагически. В описании наряда писательницы непосредственно перед ее гибелью автор вопроса упомянул название романа, заменив в нем последнее слово на слово "камней". Назовите этот роман.
+Ответ: "Карман, полный ржи".
+Зачёт: "A Pocket Full of Rye".
+Комментарий: Вульф утопилась, предварительно наполнив карман камнями.</t>
+  </si>
+  <si>
+    <t>Вопрос 29: В 90-х годах клубы НХЛ начали сотрудничать с российскими командами. Так, ЦСКА после заключения договора с Питтсбургом стал называться "Русскими пингвинами". Сотрудничать с одной из российских команд намеревался и Майкл Илич. Назовите эту команду и клуб НХЛ, которым владел Илич.
+Ответ: "Крылья Советов", "Детройт Ред Уингз".</t>
+  </si>
+  <si>
+    <t>Вопрос 30: Поэт Леонид Кузубов посвятил Курской битве стихотворение, в котором есть строки: «Броня в броню, рвануло в небо пламя!» и «Горели танки жаркими кострами». Автор англоязычной статьи о Курской битве Майкл Пек едва ли был знаком со стихами Кузубова и для передачи схожего образа процитировал в своей статье… Какого англичанина?
+Ответ: [Уильяма] Блейка.
+Зачёт: по фамилии.
+Комментарий: в Курской битве участвовали танки «Тигр», а для образа горящего тигра весьма уместно процитировать знаменитое стихотворение Блейка: «Tyger, Tyger burning bright…». Ещё одно неожиданное сходство заключается в том, что оба стихотворения начинаются с лексического повтора: «Броня в броню...» у Кузубова и «Tyger, Tyger...» у Блейка.</t>
+  </si>
+  <si>
+    <t>Вопрос 9: Внимание, словами КАЖЕТСЯ НЕПРИВЫЧНЫМ мы заменили два других слова.
+    Кинообозреватель Вадим Рутковский замечает, что фильм "Монтевидео — божественное видЕние" киноману КАЖЕТСЯ НЕПРИВЫЧНЫМ. В каком фильме герой КАЖЕТСЯ НЕПРИВЫЧНЫМ героине?
+Ответ: "Андалузский пес".
+Комментарий: КАЖЕТСЯ НЕПРИВЫЧНЫМ = режет глаз.</t>
+  </si>
+  <si>
+    <t>Вопрос 12: В постмодернистской пародии на пьесу "Ричард III" Эдвард расстраивается, что его после смерти не слушают, и упоминает о планах переезда. Ответьте абсолютно точно: куда именно?
+Ответ: Эльсинор.
+Зачёт: Замок Эльсинор.
+Комментарий: И, как и подобает в постмодернистском тексте, Эдвард становится тенью — видимо, тенью отца Гамлета.</t>
   </si>
 </sst>
 </file>
@@ -363,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -400,9 +340,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -706,12 +643,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>2</v>
@@ -720,12 +657,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="278.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="7">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>4</v>
@@ -734,12 +671,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="318" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="7">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>6</v>
@@ -748,12 +685,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>7</v>
@@ -762,71 +699,69 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="10">
-        <v>45574</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="14">
+        <v>45580</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="13">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>45575</v>
+        <v>45581</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="9">
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="318" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="7">
-        <v>45575</v>
+        <v>45581</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="9">
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="133.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>45575</v>
+        <v>45581</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" s="9">
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="265.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="7">
-        <v>45575</v>
+        <v>45581</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" s="9">
         <v>24</v>
@@ -837,62 +772,62 @@
         <v>9</v>
       </c>
       <c r="B11" s="10">
-        <v>45575</v>
+        <v>45581</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="12"/>
     </row>
-    <row r="12" spans="1:4" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="7">
-        <v>45576</v>
+        <v>45582</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="9">
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="304.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>45576</v>
+        <v>45582</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D13" s="9">
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>45576</v>
+        <v>45582</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D14" s="9">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="331.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="318" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>45576</v>
+        <v>45582</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D15" s="9">
         <v>164</v>
@@ -903,62 +838,62 @@
         <v>14</v>
       </c>
       <c r="B16" s="10">
-        <v>45576</v>
+        <v>45582</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="1:4" ht="278.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>45577</v>
+        <v>45583</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D17" s="9">
         <v>178</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="291.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="7">
-        <v>45577</v>
+        <v>45583</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="9">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="291.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>45577</v>
+        <v>45583</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D19" s="9">
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="7">
-        <v>45577</v>
+        <v>45583</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D20" s="9">
         <v>171</v>
@@ -969,291 +904,201 @@
         <v>19</v>
       </c>
       <c r="B21" s="10">
-        <v>45577</v>
+        <v>45583</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="1:4" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="7">
-        <v>45578</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="D22" s="9">
         <v>179</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="7">
-        <v>45578</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>10</v>
-      </c>
       <c r="D23" s="9">
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="7">
-        <v>45578</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="D24" s="9">
         <v>172</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="7">
-        <v>45578</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="D25" s="9">
         <v>165</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="10">
-        <v>45578</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="7">
-        <v>45579</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="D27" s="9">
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="7">
-        <v>45579</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>15</v>
-      </c>
       <c r="D28" s="9">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="7">
-        <v>45579</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="D29" s="9">
         <v>167</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="7">
-        <v>45579</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="D30" s="9">
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="10">
-        <v>45579</v>
-      </c>
-      <c r="C31" s="11"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
       <c r="D32" s="9">
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
       <c r="D33" s="9">
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
       <c r="D34" s="9">
         <v>167</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
       <c r="D35" s="9">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="11"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
       <c r="D37" s="9">
         <v>175</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="8"/>
       <c r="D38" s="9">
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
       <c r="D39" s="9">
         <v>162</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
       <c r="D40" s="9">
         <v>161</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
       <c r="D42" s="9">
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
       <c r="D43" s="9">
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="8"/>
       <c r="D44" s="9">
         <v>172</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
       <c r="D45" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" s="10">
-        <v>45573</v>
-      </c>
-      <c r="C46" s="11"/>
       <c r="D46" s="12"/>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -27,98 +27,599 @@
     <t>Question</t>
   </si>
   <si>
-    <t>Вопрос 4:
-https://db.chgk.info/images/db/20121062.jpg
-    Сначала мы желали спрятать на раздаточном материале больше, но скрытая от вас заглавная "героиня" вырвала гвозди, которыми была прибита. Назовите эту "героиню".
-Ответ: Шагреневая кожа.
-Комментарий: После выполнения желаний шагреневая кожа уменьшалась в размерах, и ничто не могло остановить процесс сокращения.</t>
-  </si>
-  <si>
-    <t>Вопрос 9: "Побережем осла, если хотим дожить до старости!". Из какого романа XIX века взята эта образная ремарка автора?
-Ответ: "Шагреневая кожа".
-Комментарий: Шагреневая кожа была выделанной особым образом ослиной шкурой. Как известно, она сжималась при каждом выполненном желании владельца, сокращая его жизнь.</t>
-  </si>
-  <si>
-    <t>Вопрос 3: Основная черта гипертекста — нелинейность повествования. Энрике Шмидт, рассуждая о будущем литературных гипертекстов, задается вопросом: "Цветут ли ИКСЫ?". Назовите ИКС тремя словами.
-Ответ: Сад расходящихся тропок.
-Комментарий: "Сад расходящихся тропок" — рассказ Борхеса, представляющий собой классический пример литературного гипертекста.</t>
-  </si>
-  <si>
-    <t>Вопрос 28: Кому посвящён объект площадью более шести тысяч квадратных метров, созданный основателем компании «Минотавр Дизайн» в южноамериканском городе Сан-Рафаэ́ль?
-Ответ: [Хо́рхе Луи́су] Бо́рхесу.
-Зачёт: по фамилии.
-Комментарий: в аргентинском городе Сан-Рафаэль находится «Лабиринт Борхеса», в котором есть множество расходящихся тропок. «Сад расходящихся тропок» – знаменитый рассказ Хорхе Луиса Борхеса.</t>
-  </si>
-  <si>
-    <t>Вопрос 3: Дуплет.
-    1. Евгения Гинзбург пишет, что для девушки, выросшей в Харбине и вернувшейся позже в Советский союз, "потери бдительности", "примиренчество" и "гнилые либерализмы" звучали ЭТИМ. Назовите ЭТО.
-    2. Крупнейший в истории проект, призванный защитить северные районы одной страны от нашествия пустыни, называется "Зеленая ОНА". Назовите ЕЕ двумя словами.
+    <t xml:space="preserve">Вопрос 204: Музыкант Сергей Курёхин полагал, что она звучит довольно сумбурно, слишком шипяще. Назовите ЕЕ.
+Ответ: Фамилия Шостакович.
+Комментарий: Как известно, музыка Шостаковича была жестоко раскритикована в статье "Сумбур вместо музыки".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 32: В 30-х годах XIX века вышла статья, в которой работа Лобачевского о неевклИдовой геометрии называлась бессмысленной и запутанной. По выражению автора вопроса, в статье фактически заявлялось, что работа Лобачевского – это ПРОПУСК математики. Заполните ПРОПУСК двумя словами.
+Ответ: сумбур вместо.
+Комментарий: спустя 100 лет после разгрома Лобачевского в российском журнале уже в советской прессе разгромлен будет музыкальный гений ШостакОвич – его работы назовут «сумбуром вместо музыки».
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 7: Биограф ЛОрел Фей пишет, что известный человек после события 1936 года в шутку обещал назвать новорождённую дочь Субмариной. Мы не спрашиваем, какое слово в этом вопросе мы изменили. Назовите этого человека.
+Ответ: Дмитрий Шостакович.
+Комментарий: Он шутил, что мог бы назвать дочь Сумбуриной. Так, по некоторым сведениям, Шостакович реагировал на статью "Сумбур вместо музыки".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 5:
+https://db.chgk.info/images/db/20120035.jpg
+    Мы хотели сделать музыкальный вопрос, но не знаем, смогут ли организаторы воспроизвести аудиофрагмент. Поэтому вопрос будет с раздаточным материалом.
+    Название розданной вам картины художника Виктории Чернобыльской состоит из одного слова. Напишите это название.
+Ответ: "Сумбур".
+Комментарий: Мы раздали "Сумбур" вместо музыки.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 4: Согласно этимологическому словарю, слово "МУЗЫКА" родственно глаголу калмыцкого происхождения, означающему "взбивать воду", "рыхлить снег". Какое слово мы заменили словом "музыка"?
+Ответ: Сумбур.
+Комментарий: Вот такой "сумбур вместо музыки".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 4: В романе Лукьяненко "Ночной дозор" один из героев угощает друга неким "крутым" спиртным напитком, который производится, в частности, на Московском Межреспубликанском винодельческом заводе. По словам героя, это напиток является "русским ответом" его всемирно известному импортному аналогу. Назовите оба напитка — и российский, и импортный.
+Ответ: Коньяки "Кутузов" и "Наполеон".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 10: Вопреки распространенному мнению, ЭТО получило название не в честь ПЕРВОГО, а в память о ТРЕТЬЕМ, много сделавшем для становления системы классификации того, что считается гордостью страны. Назовите их обоих.
+Ответ: Наполеон I и Наполеон III.
+Зачёт: Наполеоны.
+Комментарий: Речь идет о коньяках. Наполеон III был знатоком французского виноделия.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 28: Хотя компания Courvoisier была основана только в 1835 году, по легенде, несколько бочек напитка в своё время оказались на НЁМ. ОН получил своё название в честь человека, умершего в IV веке. Назовите ЕГО тремя словами.
+Ответ: остров святой Елены.
+Зачёт: точный ответ.
+Комментарий: Коньяк якобы пришёлся настолько по вкусу Наполеону I, что тот повёз его с собой в изгнание.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 56: Это чуть ли не единственная ситуация, в которой не только совершенно официально и без всяких стеснений ущемляются права черных, причем черные не возражают, ведь иначе никакое искусство не поможет белым спастись. А одним из первых запретов стало запрещение черным делать "вилки". А из чего они эти "вилки" делают?
+Ответ: Из камней рэндзю.
+Зачёт: Из фишек рэндзю.
+Комментарий: В рэндзю первый ход, согласно правилам, принадлежит черным, ну, как и в любых вариантах "крестиков-ноликов", выигрывает тот, кто сделал первый ход — конечно, если оба игрока опытные. :-)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9:  Интересно, что в 2016 году в ходе выставочного матча обладатель наивысшего рейтинга в рэндзю Yixin [йи синь] проиграл не самому сильному белому игроку Дмитрию Епифанову. В одном из слов предыдущего предложения мы пропустили три буквы. Напишите это слово в исходном виде.
+Ответ: Белковому.
+Комментарий: Yixin [йи синь] — обладатель наивысшего рейтинга Эло в рэндзю среди компьютерных программ. В прошедшем в Москве выставочном матче белковый спортсмен Дмитрий Епифанов одержал победу над программой. В отличие от игры го, в рэндзю компьютерные программы еще не в состоянии уверенно обыгрывать людей.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 5:
+https://db.chgk.info/images/db/20180146.jpg
+    Этот человек не удержался от того, чтобы создать свою версию известной оперы. Назовите и этого человека, и главного героя оперы.
+Ответ: [Карл] Орф, Орфей.
+Комментарий: Фотографии показывают оборачивающегося Карла Орфа. Аналогичное движение стало поворотным в судьбе мифического музыканта Орфея, не удержавшегося от взгляда на Эвридику. Карл Орф создал свою версию оперы Монтеверди об Орфее.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 11: Долгое время он придерживался националистических убеждений и поддержал приход к власти Гитлера, однако изменил свое отношение, когда начались гонения на церковь. "Больше мы не можем хранить молчание, повеленное человеком... Господь велит нам говорить!" — заявил он на своем последнем выступлении. С какого слова начинается каждое предложение его самого известного произведения?
+Ответ: Когда.
+Зачёт: Als.
+Комментарий: Речь идет о протестантском теологе, пасторе Мартине Нимёллере, авторе знаменитого стихотворения:
+    Когда нацисты пришли за коммунистами, я молчал, я же не был коммунистом. Когда они пришли за социалистами, я молчал, я же не был социал-демократом. Когда они пришли за профсоюзными деятелями, я молчал, я же не член профсоюза. Когда они пришли за евреями, я молчал, я же не был евреем. Когда они пришли за мной, больше не было никого, кто бы мог протестовать.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 6 Американка камбоджи́йского происхождения Лун Ун написала воспоминания о правлении красных кхмеров, во времена которых последовательно пострадали разные слои населения. Название книги перекликается с известной цитатой. Назовите автора этой цитаты.
+Ответ: [Мартин] Нимёллер.
+Комментарий: Книга Лун Ун называется «Сначала они убили моего отца». В США распространен вариант цитаты Нимёллера, 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 29 Мартин Нимёллер говорил, что не был ни коммунистом, ни социал-демократом, ни ИКСОМ. А за что, согласно известному произведению, с ИКСОВ требовали десять копеек?
+Ответ: За посещение Провала.
+Зачёт: По смыслу.
+Комментарий: Мартин Нимёллер также говорил, что не был членом профсоюза. Остап Бендер взимал плату за посещение Провала ("Членам профсоюза — 10 копеек и не членам профсоюза — 30 копеек").
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 14: Прослушайте список:
+    — Альфред Андерш, коммунист;
+    — Адольф Мейслингер, социал-демократ;
+    — Альберт Росхауптер, профсоюзный деятель;
+    — Бруно Беттельгейм, еврей.
+    В один ряд с этими узниками Дахау можно поставить уроженца Липштадта, ставшего в 1967 году лауреатом Международной Ленинской премии. Назовите его фамилию.
+Ответ: Нимёллер.
+Комментарий: Немецкий пастор, автор известного стихотворения: "Когда нацисты пришли за коммунистами, я молчал, я же не коммунист. / Потом они пришли за социал-демократами, я молчал, я же не социал-демократ. / Потом они пришли за профсоюзными деятелями, я молчал, я же не член профсоюза. / Потом они пришли за евреями, я молчал, я же не еврей. / А потом они пришли за мной, и уже не было никого, кто бы мог протестовать". Нимёллер, как и Андерш, Мейслингер, Росхауптер и Беттельгейм, в свое время был интернирован в Дахау.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 12: Какая трава, по справедливому замечанию Айзека АзИмова, может прервать нить жизни?
+Ответ: Белладонна.
+Зачёт: Красавка, сонная одурь, красуха, бешеная ягода, бешеная вишня, атропа.
+Комментарий: Нить жизни прерывала мойра Атропос, в честь которой Карл Линней и дал латинское название белладонне. Это название более известно по выделенному из белладонны яду — атропину.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: Остроумный Иван Матвеев объясняет одно из свойств философского камня тем, что его владелец способен победить ЕЕ. Напишите ЕЕ имя.
+Ответ: Атропос.
+Комментарий: Философский камень способен победить ножницы, находящиеся в руках Атропос — мойры, перерезающей нить человеческой судьбы.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 12: На картине Рубенса "Судьба Марии Медичи" ВЕСЫ ФЕМИДЫ опущены, чтобы подчеркнуть привилегированный и бессмертный характер жизни королевы. Что мы заменили словами "ВЕСЫ ФЕМИДЫ"?
+Ответ: Ножницы Атропос.
+Зачёт: Ножницы мойры; ножницы судьбы.
+Комментарий: Нитью судьбы королевы на картине занимаются мойры.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 13: Историк пишет, что, по иронии судьбы, когда ОНА попала на предназначенное ей место, над крепостью уже снова развевались голландские флаги. Назовите ЕЕ автора.
+Ответ: [Диего] Веласкес.
+Комментарий: Она — картина "Сдача Бреды". Бреда перешла к испанцам в 1625 году. Картина Веласкеса датируется 1635 годом. Формально Бреда снова перешла к голландцам в 1637 году, но в реальности на пару лет раньше. К тому моменту, когда написанная Веласкесом по заказу картина заняла свое место в одной из королевских резиденций, над крепостью Бреда уже снова развевались голландские флаги.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 2: В 1982 году этой женщине при встрече подарили весьма невзрачный на вид букетик цветов. Назовите эту женщину, имя и фамилия которой начинаются на одну и ту же букву.
+Ответ: [Светлана] Савицкая.
+Комментарий: При прибытии Савицкой на космическую станцию "Салют-7" находящиеся там коллеги-космонавты вручили ей букетик из семи невзрачных цветов, которые им удалось вырастить в космосе в рамках научного эксперимента.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: 156. Тур Буманн-Ларсен сравнил "Норвегию" с выброшенным на берег китовым скелетом. Назовите выпускника инженерно-математического факультета Неаполитанского университета, бывшего в "Норвегии" за несколько дней до того.
+Ответ: Умберто Нобиле.
+Комментарий: Первая экспедиция на Северный полюс (под руководством Нобиле и Амундсена). Демонтированный после экспедиции дирижабль "Норвегия" являл собой жалкое зрелище. Кстати, Буманн-Ларсен к полярнику Рисер-Ларсену не имеет никакого отношения. :-)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: Психологи называют склонность к прокрастина́ции ИМ. Назовите ЕГО двумя словами на одну букву.
+Ответ: синдром Скарлетт
+Зачёт: был засчитан спорный "синдром студента".
+Комментарий: прокрастинация — это склонность откладывать дела. Героиня Маргарет Ми́тчелл говорила “Я подумаю об этом завтра”.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 48: На этот вопрос вам придётся ответить сейчас. Андрей Рубанов считает её слова проявлением не легкомыслия, а веры в будущее. Назовите её.
+Ответ: Скарлетт (О’Хара).
+Комментарий: фраза «Я подумаю об этом завтра» свидетельствует о безоговорочной вере в то, что завтрашний день наступит, что в условиях Гражданской войны было неочевидно. А вам над вопросом пришлось думать сегодня.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 4: Дуплет.
+    1. Винтовка винчестер сыграла важную роль в войне Севера и Юга. Публицист Аркадий Драгомащенко называет жертв этой войны ПРОПУСК и винчестером. Какие два слова мы пропустили?
+    2. Уставший автор оставил на некоторое время попытки отредактировать только что прозвучавший вопрос. Какой фразой он выразил свои намерения?
 Ответ:
-    1. Китайская грамота.
-    2. Китайская стена.
-Комментарий:
-    1. Девушка работала на Китайской Восточной железной дороге и вернулась в СССР после продажи дороги Китаю.
-    2. По аналогии с Великой китайской стеной, которая должна была защитить север Китая от нашествия кочевников.</t>
-  </si>
-  <si>
-    <t>Вопрос 12: Вину на себя взял француз Робер Юбер, из-за чего многие заподозрили заговор папистов. И лишь много позже официально был признан факт нарушения техники безопасности. А в чем обвиняли Юбера?
-Ответ: В Великом лондонском пожаре.
-Зачёт: В Большом лондонском пожаре; в лондонском пожаре 1666 года.
-Комментарий: Как и большинство пожаров, тот возник из-за неосторожного обращения с огнем (в пекарне), а Юбер был просто одержим манией величия.</t>
-  </si>
-  <si>
-    <t>Вопрос 2: В статье о НЕЙ в качестве "первопроходцев" названы наркомы Александра Коллонтай и Павел Дыбенко. Другую ЕЕ планировалось описать еще в первой книге. Назовите ЕЕ двумя словами.
-Ответ: Красная свадьба.
-Комментарий: В противовес церковному венчанию в 1920-х годах стали практиковаться т.н. "красные свадьбы". Во втором случае речь идет о событиях эпопеи Джорджа Р.Р. Мартина.</t>
-  </si>
-  <si>
-    <t>Вопрос 5: Персонаж одного фэнтезийного рассказа пришел в гости к женщине, но увидел на пороге дома дракона. Через некоторое время, в то время как персонаж пил с женщиной чай, его начал мучить вопрос. Назовите любого из тех, кто фигурирует в похожем вопросе, возникшем до нашей эры.
+    1. Унесенные ветром.
+    2. "Я подумаю об этом завтра".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 15: Одна из глав романа Туве Янссон "Муми-папа и море" называется "Западный ветер". В конце главы уставший герой, отгоняя мрачные мысли, произносит фразу, известную нам благодаря другому литературному персонажу. Назовите пять слов, ее составляющие.
+Ответ: Я подумаю об этом завтра.
+Комментарий: Знаменитая реплика героини романа "Унесенные ветром".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 26: Когда будущий писатель Тони Броудбент догадался, что Санта-Клаусом был его папа, то получил в подарок книжку. Памятная табличка тому, чья фамилия была на книжке, есть на смотровой площадке... Возле чего?
+Ответ: Рейхенбахского водопада
+Комментарий: чтобы сделать такой вывод, Броудбент уже в юном возрасте проявил наблюдательности и логическое мышление. Это подвигло родителей подарить будущему автору детективов книгу о Шерлоке Холмсе.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 5: Около какого объекта, расположенного на территории Швейцарии, в 1899 году был открыт фуникулёр?
+Ответ: Рейхенбахский водопад.
+Комментарий: После публикации "Последнего дела Холмса", в котором описана схватка великого сыщика с профессором Мориарти у Рейхенбахского водопада, количество туристов, приезжающих посмотреть на водопад, резко увеличилось, и возникла необходимость в канатной дороге.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 19: В одном эпизоде сериала «Элементарно» после длительной борьбы все же удаётся победить злодея. Название этого эпизода «ПРОПУСК падает». Напишите пропущенную нами фамилию этого злодея.
+Ответ: Ра́йхенбах.
+Зачёт: Рейхенба́х.
+Комментарий: эпизод называется «Reichenbach Falls» [райхенбах фоллс] — отсылка к классическому эпизоду у Рейхенбахского водопада.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 33: Ниро Вульф говорил, что готов к смертельной схватке с криминальным миром. Рекс СтАут отмечал, что на пейзаже в кабинете Вульфа изображён именно ОН. Назовите ЕГО двумя словами.
+Ответ: РейхенбАхский водопад.
+Комментарий: при необходимости Ниро Вульф готов дать смертельный бой криминальному миру, подобно тому как Шерлок Холмс рисковал жизнью, вступив в схватку с Мориарти на краю Рейхенбахского водопада. В самих книгах о Вульфе не сообщается, какой именно водопад изображён на картине, но в интервью Стаут уточнил, что по его задумке это именно Рейхенбахский водопад.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 18: Действие компьютерной игры "Assassin's Creed Origins" происходит в Египте. Если долго бродить по пустыне, то можно начать видеть миражи оазисов, слышать звуки битвы, встретить кучу летающих насекомых. Также можно встретить АЛЬФУ. Какое устойчивое выражение из двух слов мы заменили АЛЬФОЙ?
+Ответ: Неопалимая купина.
+Комментарий: Библейские аллюзии пронизывают игру. Летающие насекомые — одна из казней египетских — нашествие саранчи.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 47: Рассказывают, что Джон Браунинг придумал отводить пороховые газы, когда открыл огонь на стрельбище и увидел дрожащие ветви кустов в дыму. Забавно, что вторым именем Браунинга было... Какое?
+Ответ: Мозес.
+Зачёт: Моисей.
+Комментарий: "Не зря его второе имя было Мозес, — отмечает историк оружия Джеймс Баллу, — подобно тому как Моисею пришло озарение из Неопалимой купины, на Браунинга, смотрящего на дрожащие ветви кустов в пороховом дыму тоже снизошло озарение".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 8:
+https://db.chgk.info/images/db/20140812.jpg
+    На розданной вам фотографии — монастырь святой Екатерины, расположенный у подножия горы Синай. На фотографии мы закрыли ИКС, который стоит там на всякий случай. Назовите ИКС словом с двумя корнями.
+Ответ: Огнетушитель.
+Комментарий: На фотографии Неопалимая КупинА — горящий куст, из которого Господь говорил с Моисеем. На случай повторения чуда весьма уместен огнетушитель.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: После того, как немцы обнародовали материалы о Катынском расстреле, польский политик Владислав Сикорский потребовал от Черчилля разрыва отношений с СССР. 4 июля 1943 года Сикорский погиб в небе над Гибралтаром. Интересно, что в это же время в Гибралтаре находился ОН. Кто ОН?
+Ответ: Ким Филби.
+Комментарий: После Сталинградской битвы стало понятно, что Советский Союз — ключ к победе союзников. Требования Сикорского угрожали недовольством общественного мнения в странах запада, что было неприемлемо ни для Сталина, ни для Черчилля. Ким Филби был двойным агентом Ми-6 и советской разведки, и, возможно, был причастен к смерти Сикорского — по приказу какого-то из начальств.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 24: Шарль Бодлер, говоря о бесчисленных наслоениях мыслей и образов, ни одно из которых на самом деле не погибло, называет человеческий мозг естественным ИМ. Назовите ЕГО словом греческого происхождения.
+Ответ: палимпсест.
+Комментарий: Человеческая память, хранящая множество воспоминаний, действительно чем-то похожа на палимпсест — рукопись, написанную на уже бывшем в употреблении материале, в которой иногда удается прочесть предыдущие записи. Организаторы турнира надеются, что память об Андрее тоже будет долгой.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 7: Цитата из Википедии: "Сполии (лат. spolia, букв. "трофеи") — элементы декора, особенно колонны, которые в поздней античности и раннем средневековье выламывались из древних сооружений (как правило, языческих храмов) и использовались при строительстве новых зданий (как правило, храмов христианских)". После статьи о сполиях помещена ссылка на статью, названную десятибуквенным греческим словом. Напишите это слово.
+Ответ: Палимпсест.
+Комментарий: Рукопись, написанная поверх соскобленного текста.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 7: Герой Роджера Желязны опасается, что другие боги найдут его, прочтя воспоминания случайного свидетеля его божественной сущности. Его напарник считает, что проблему можно решить, убедив свидетеля в другой точке зрения на произошедшие события. При этом напарник упоминает ИКС. Алкогольным ИКСОМ называют частичную потерю памяти, вызванную злоупотреблением спиртными напитками. Какое слово греческого происхождения мы заменили на ИКС?
+Ответ: Палимпсест.
+Комментарий: Рукопись на пергаменте либо папирусе поверх смытого или соскобленного текста. Воспоминания о периоде пребывания в состоянии алкогольного опьянения словно бы перезаписываются более новыми.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 13: Один из аргументов в пользу того, что глаголица появилась раньше кириллицы, — то, как выглядят ОНИ. Первый корень в ИХ названии переводится как "опять". Назовите ИХ.
+Ответ: ПалимпсЕсты.
+Комментарий: Ни на одном палимпсесте глаголица не заменяет кириллицу — везде удален глаголический текст и вместо него написан кириллический. Название происходит от πάλιν (палим) — опять и ψηστός (псестос) — соскобленный.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 11: [Ведущему: текст раздатки не зачитывать.]
+Раздаточный материал
+    РИККИ-ТИГККИ-ТАВИ
+    Говоря о трудностях адаптации, Виктор Егоров пишет, что некоторые эмигранты чувствуют на себе РИККИ-ТИГККИ-ТАВИ. Какие три слова мы заменили на "РИККИ-ТИГККИ-ТАВИ"?
+Ответ: Бремя беглого человека.
+Комментарий: И "Рикки-Тикки-Тави", и "Бремя белого человека" написал Киплинг. В замене мы добавили в имя мангуста лишнюю букву "г", а Виктор Егоров добавил букву "г" в слово "белого".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 2: На одном из банкетов диктатор Уганды Иди Амин появился в кресле, которое несли четыре английских бизнесмена. Амин дал этому перформансу ироническое название, которое читатели журнала "МэкКлюрс" впервые увидели более века назад. Воспроизведите это название.
+Ответ: Бремя белого человека.
+Зачёт: White man's burden.
+Комментарий: Так африканский диктатор издевался над знаменитой доктриной британского колониализма, воспетой Р. Киплингом.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 31 В одной существующей книге рассказывается, что семейное дерево это не ИГРЕК, а неухоженные заросли густого кустарника. Другой ИГРЕК был написан в середине прошлого века. Назовите ИГРЕК тремя словами.
+Ответ: Сад расходящихся тропок
+Комментарий: автор научно-популярной книги пишет, что человеческая генеалогия это не сад расходящихся тропок, а запутанные заросли густого кустарника. В сборнике Бо́рхеса «Сад расходящихся тропок» важную роль играют сюжеты несуществующих книг. Могла помочь и визуальная схожесть ИГРЕКА с расходящейся тропкой.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 5: Герой комикса "Неамериканские гладиаторы" называет участников соревнований "идущие ПРОПУСК". "ПРОПУСК" — название интернет-магазина по продаже картриджей и бумаги. Заполните пропуск двумя словами.
+Ответ: в расход
+Комментарий: неамериканские гладиаторы идут не на смерть, а — что более прозаично — в расход. Картриджи и бумага — расходные материалы.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 12: Герой одного фильма решает поехать в Швейцарию, потому что в Англии человек, согласившийся ему помочь, может на много лет сесть в тюрьму. В статье об этом фильме есть ссылка на калифорнийский закон "О праве ПРОПУСК". Кто упомянут в известном выражении, в котором есть два пропущенных слова?
+Ответ: Цезарь.
+Зачёт: Идущие [на смерть].
+Комментарий: Речь в вопросе идет об эвтаназии, которая запрещена в Англии, но разрешена в Швейцарии. Пропущенные слова — "на смерть", а известная фраза — обращение гладиаторов к императору: "Ave, Caesar, morituri te salutant" [Аве цЕзарь моритУри те салЮтант] — "Славься, Цезарь, идущие на смерть приветствуют тебя".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 8
+ Гурман Александр Генис готовит баранину по-турецки. "Как только мясо будет готово, ты (пропуск) на полчаса" — пишет Генис. "На полчаса — потому что баранину надо есть, пока не остыла" — уточняет он. Восстановите пропущенное существительное.
+Ответ: Калиф.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 5: Внимание, слово "план" в вопросе — замена.
+    После смерти Феллини остался дневник, в который режиссер записывал свои планы. Позднее по этим планам даже сняли несколько фильмов. Широко известна дилемма, связанная с планом одного "чиновника". Какое животное фигурирует в этом плане?
 Ответ: Бабочка.
-Зачёт: Чжуан-цзы.
-Комментарий: Дракон превращается в женщину, и героя начинает мучить вопрос, кто же перед ним — женщина, которая умеет превращаться в дракона, или дракон, умеющий превращаться в женщину. Легенда гласит, что однажды философ Чжуан-цзы заснул, и ему приснилось, что он бабочка, которой снится, что она Чжуан-цзы. Проснувшись, философ долго не мог понять, кто же он на самом деле — Чжуан-цзы или бабочка.</t>
-  </si>
-  <si>
-    <t>Вопрос 1: В романе НатАниэля ГОторна "Алая буква" осуждается пуританское общество Новой Англии. Еще в молодости Готорн несколько изменил фамилию, полученную при рождении, чтобы скрыть родство с одним из предков, который председательствовал... Ответьте абсолютно точно, где именно.
-Ответ: На суде над салемскими ведьмами.
-Комментарий: При рождении Готорн получил фамилию Гаторн, но отвращение к предку побудило ее изменить (добавить "w"). Салемский процесс — пример религиозного мракобесия пуритан Новой Англии.</t>
-  </si>
-  <si>
-    <t>Вопрос 4: Рекламу компании "Nike", в которой ОН называет себя патроном в обойме, затем пришлось срочно снять с эфира. Назовите ЕГО.
-Ответ: [Оскар] ПистОриус.
-Комментарий: Знаменитый южноафриканский спортсмен застрелил свою девушку, в результате клип стал выглядеть несколько странно.</t>
-  </si>
-  <si>
-    <t>Вопрос 7: В фильме "Перси Джексон и Море чудовищ" показано, как Зевс неким образом наказал Диониса. Назовите топоним, известный благодаря случаю, обратному этому наказанию.
-Ответ: Кана [Галилейская].
-Комментарий: У наказанного Диониса вино превращалось в воду. В Кане Галилейской Иисус превращал воду в вино.</t>
-  </si>
-  <si>
-    <t>Вопрос 13: Жизнь Вирджинии Вульф окончилась трагически. В описании наряда писательницы непосредственно перед ее гибелью автор вопроса упомянул название романа, заменив в нем последнее слово на слово "камней". Назовите этот роман.
-Ответ: "Карман, полный ржи".
-Зачёт: "A Pocket Full of Rye".
-Комментарий: Вульф утопилась, предварительно наполнив карман камнями.</t>
-  </si>
-  <si>
-    <t>Вопрос 29: В 90-х годах клубы НХЛ начали сотрудничать с российскими командами. Так, ЦСКА после заключения договора с Питтсбургом стал называться "Русскими пингвинами". Сотрудничать с одной из российских команд намеревался и Майкл Илич. Назовите эту команду и клуб НХЛ, которым владел Илич.
-Ответ: "Крылья Советов", "Детройт Ред Уингз".</t>
-  </si>
-  <si>
-    <t>Вопрос 30: Поэт Леонид Кузубов посвятил Курской битве стихотворение, в котором есть строки: «Броня в броню, рвануло в небо пламя!» и «Горели танки жаркими кострами». Автор англоязычной статьи о Курской битве Майкл Пек едва ли был знаком со стихами Кузубова и для передачи схожего образа процитировал в своей статье… Какого англичанина?
-Ответ: [Уильяма] Блейка.
-Зачёт: по фамилии.
-Комментарий: в Курской битве участвовали танки «Тигр», а для образа горящего тигра весьма уместно процитировать знаменитое стихотворение Блейка: «Tyger, Tyger burning bright…». Ещё одно неожиданное сходство заключается в том, что оба стихотворения начинаются с лексического повтора: «Броня в броню...» у Кузубова и «Tyger, Tyger...» у Блейка.</t>
-  </si>
-  <si>
-    <t>Вопрос 9: Внимание, словами КАЖЕТСЯ НЕПРИВЫЧНЫМ мы заменили два других слова.
-    Кинообозреватель Вадим Рутковский замечает, что фильм "Монтевидео — божественное видЕние" киноману КАЖЕТСЯ НЕПРИВЫЧНЫМ. В каком фильме герой КАЖЕТСЯ НЕПРИВЫЧНЫМ героине?
-Ответ: "Андалузский пес".
-Комментарий: КАЖЕТСЯ НЕПРИВЫЧНЫМ = режет глаз.</t>
-  </si>
-  <si>
-    <t>Вопрос 12: В постмодернистской пародии на пьесу "Ричард III" Эдвард расстраивается, что его после смерти не слушают, и упоминает о планах переезда. Ответьте абсолютно точно: куда именно?
-Ответ: Эльсинор.
-Зачёт: Замок Эльсинор.
-Комментарий: И, как и подобает в постмодернистском тексте, Эдвард становится тенью — видимо, тенью отца Гамлета.</t>
+Комментарий: План — сон. Чиновник — Чжуан-цзы (его называли также Мэн-ши — чиновник Мэн), которому однажды приснилось, что он бабочка. И он не мог понять то ли он философ, которому снится бабочка, то ли бабочка, которой снится, что она философ.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 2:
+https://db.chgk.info/images/db/20160494.jpg
+    Перед вами фрагмент постера к экранизации произведения, которое появилось во время расцвета движения красных кхмеров. Назовите это произведение.
+Ответ: "Дети кукурузы".
+Комментарий: Ряды красных кхмеров пополнялись, в основном, подростками 12-15 лет. В рассказе Стивена Кинга "Дети кукурузы" подростки захватывают власть в городе и расправляются с теми, кому исполнилось 18 лет.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 27: Говоря о вкладе Аркадия Пла́стова в картину «Опять двойка», Софья Багдаса́рова вспоминает произведение 1889 года. Назовите автора этого произведения.
+Ответ: (Иван) Шишкин.
+Зачёт: (Константин) Савицкий.
+Комментарий: по словам знавших Фёдора Решетникова людей, Пластов написал собаку на знаменитой картине, что перекликается с тем, как Савицкий дорисовал медведей на шедевре Шишкина.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 2:  Исаак Фридберг предложил разбить легендарную книгу на две части: Книгу о ПЕРВОЙ и Книгу о ВТОРОЙ. Первую обычно используют добровольно, а вторую — порой, увы, вынужденно. Назовите ПЕРВУЮ и ВТОРУЮ.
+Ответ: Вкусная пища, здоровая пища.
+Комментарий: Речь шла о "Книге о вкусной и здоровой пище".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 4: С 70-х годов XX века ЕЕ стали называть антисоветской, поскольку ОНА напоминала о том, что когда-то в стране были камчатский краб, астраханский осетр и тамбовский окорок. Назовите ЕЕ шестью словами.
+Ответ: "Книга о вкусной и здоровой пище".
+Комментарий: Когда книга только создавалась, данные продукты были доступны советским гражданам, но в дальнейшем простые люди потеряли возможность купить их в магазине.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 6: В фильме Андрея Хржановского есть эпизод, где в голодные послевоенные годы маленький мальчик разговаривает о НЕЙ со Сталиным. Назовите ЕЕ четырьмя словами.
+Ответ: Вкусная и здоровая пища.
+Комментарий: Этим мальчиком был, кстати, маленький Иосиф Бродский. А в знаменитой "Книге о вкусной и здоровой пище" большинство цитат принадлежало Сталину.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 268: Евгений Добренко пишет, что ОНА публиковалась в легко узнаваемых обложках салатного или кремового цветов. Назовите ЕЕ максимально точно.
+Ответ: "Книга о вкусной и здоровой пище".
+Комментарий: Цвета тоже "кулинарные".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 2: В 1746 году Василий ТатИщев был сослан в своё имение под домашний арест. Энциклопедия "Кругосвет" называет ИКС самым плодотворным в жизни Татищева. Назовите ИКС двумя словами, начинающимися на парные согласные.
+Ответ: бОлдинский период.
+Зачёт: точный ответ.
+Комментарий: как и Пушкин, Татищев самое продуктивное в творческом плане время провёл в селе БОлдино. Только имение Василия Никитича — это село Болдино Московской губернии, а Александр Сергеич свою знаменитую осень провёл в Большом Болдино Нижегородской губернии.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 31: В 1665 году Кембриджский университет был временно закрыт, и Ньютон был вынужден уехать. Говоря, о вкладе Ньютона в мировую науку Рената Ли́бина упоминает вулсторпскую ЕЕ, хотя Ньютон вернулся в университет лишь через два года. Назовите ЕЕ одним словом.
+Ответ: осень.
+Комментарий: университет был закрыт из-за эпидемии чумы, поэтому ряд прорывны́х исследований Ньютон совершил в родовом поместье Вулсторп. Более известна «болдинская осень» Пушкина, когда поэт не мог покинуть село из-за холерного карантина.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 13:
+Раздаточный материал
+    Д _ _ б _ _ _
+    Восстановите название усадьбы, в которой Василий Жуковский плодотворно провел ноябрь и октябрь 1814 года.
+Ответ: Долбино.
+Комментарий: У Пушкина была Болдинская осень, а у Жуковского — Долбинская.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 11: Благодаря ЕЙ в 1970 году для Жванецкого и его коллег смягчили цензуру и отправили на гастроли по Украине для поднятия духа жителей страны. Как известно, ОНА благотворно сказалась и на творчестве другого литератора. Назовите ЕЕ максимально точно.
+Ответ: Холера.
+Зачёт: Эпидемия холеры.
+Комментарий: Благодаря карантину по поводу эпидемии холеры случилась Болдинская осень.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 6: Согласно расхожему выражению, биржевые трейдеры ДЕЛАЮТ ЭТО. ЭТО ДЕЛАЛ заглавный герой романа. Какого автора?
+Ответ: [Александра Романовича] Беляева.
+Комментарий: Биржевые трейдеры торгуют воздухом, как и заглавный герой фантастического романа Александра Беляева "Продавец воздуха".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 8: Внимание, в вопросе есть замена.
+    За десять тысяч танзанийских шиллингов можно купить несколько бутылок местного крепкого алкоголя. Забавно, что на купюре в десять тысяч шиллингов изображен зеленый змей. Какие два слова мы заменили?
+Ответ: Розовый слон.
+Комментарий: Розовые слоны — эвфемизм для обозначения галлюцинаций, вызванных белой горячкой или алкогольным галлюцинозом. Логично, что на купюре африканской страны изображен представитель местной фауны.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 15: Во время одного из своих выступлений Сара Пэйлин назвала республиканок-феминисток МИРАЖАМИ. Ироничный заголовок статьи об этом на сайте Who2 [ху-ту] гласил: "Сара Пэйлин видит МИРАЖИ". Какие два слова мы заменили словом "МИРАЖИ"?
+Ответ: Розовые слоны.
+Зачёт: Розовые слонихи.
+Комментарий: Слон — символ республиканцев, розовый цвет — символ феминистских движений, а розовые слоны — символ галлюцинаций от алкогольного или наркотического опьянения. "Розовый слон" и "МИРаж" — известные поволжские команды.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 8: В одном из эпизодов иностранного мультсериала, несмотря на название эпизода, фигурирует вполне обычный ОН, серый, материальный, из зоопарка. Мы не спрашиваем, как называется эпизод, назовите мультсериал.
+Ответ: "Розовая пантера".
+Комментарий: Серия называется "Розовый слон". Розовый слон — эвфемизм, обозначающий галлюцинации при алкогольном опьянении.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: В мультсериале "Симпсоны" местный пьяница, увидев страшного монстра, призывает на помощь старого знакомого, который растаптывает противника. Назовите этого знакомого.
+Ответ: Розовый слон.
+Комментарий: Страшный монстр был новой для пьяницы галлюцинацией. Испугавшись, он призвал более привычную.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: По сообщению журнала "Наука и жизнь" в США начали выпуск новых струн для теннисных ракеток — более эластичных и повышающих силу удара. Их структура позаимствована в природе. А благодаря чьей гипотезе стало возможно это производство?
+Ответ: Уотсона и Крика
+Комментарий: Уотсона-Крика гипотеза (модель) — структурная модель ДНК.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 25: Искусственные нейронные сети способны научиться убирать стилевую составляющую произведения, сохраняя только его суть. Рассказывая об этом, Артур Кадурин цитирует человека, умершего в 1980 году. Назовите этого человека.
+Ответ: [Рола́н] Барт.
+Комментарий: Ролан Барт писал, что задачей критика является обнаружение Автора в произведении, а «присвоить тексту Автора — это значит как бы застопорить текст, наделить его окончательным значением». Современные модели машинного обучения способны перерабатывать классические произведения, меняя или совсем устраняя оригинальный авторский стиль.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 59: В этом вопросе словом «АЛЬФА» мы заменили два слова.
+    Книга Джима Фикса «На пике спортивной формы», популяризирующая здоровый образ жизни, вышла после АЛЬФЫ. Кто написал «АЛЬФУ»?
+Ответ: [Ролан] Барт.
+Комментарий: по злой иронии автор книги, Джим Фикс, также известный как «бегущий гуру», умер во время пробежки. А книга «На пике спортивной формы» вышла после смерти автора. Ролан Барт — автор эссе «Смерть автора», в котором высказывается предложение исследовать литературное произведение отдельно от биографии автора.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9:
+Раздаточный материал
+    1. "[Пропуск 1] утверждал, что в литературной традиции от [Пропуск 2] до XIX века описание было призвано выполнять, в основном, декоративную функцию".
+    2. "На первое апреля [Пропуск 1] разыгрывает [Пропуск 2], подсунув ему взболтанную банку пива".
+    Пропуск 1 и Пропуск 2 в обеих цитатах надо соответственно заполнить одними и теми же именами собственными.
+Ответ: Барт; Гомера.
+Комментарий: В первом случае это Ролан Барт и Гомер греческий. Во втором — Барт и Гомер Симпсоны из мультика.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: В этом вопросе АЛЬФА заменяет два слова. Уильям Уолл очень удивился, когда начал плакать над незнакомой песней. Эта история приводится в книге о паранормальных явлениях, автор которой отмечает, что за несколько лет до этого случая Уолл выжил благодаря АЛЬФЕ. Назовите номинанта на Нобелевскую премию 1968 года, в статье о котором есть раздел «АЛЬФА».
+Ответ: [Кристиан] Барнард.
+Зачёт: по фамилии с незначительными искажениями.
+Комментарий: существует псевдонаучное представление о том, что пересадка сердца может передать реципиенту черты характера его донора. Однажды Уильям Уолл неожиданно для себя заплакал над незнакомой песней «Your Love is King». Впоследствии Уолл узнал, что это была любимая песня его донора. В 1967 году уроженец ЮАР Кристиан Барнард провёл первую в мире пересадку сердца, за что на следующий год был номинирован на Нобелевскую премию в области физиологии и медицины.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 4: "Знаменитая ОНА" стала отправной точкой в творчестве американского классика. Считают, что в азиатском классике ОНА пробудила истину Дзен. Выполнив с десяток операций, каждый из вас может получить ЕЕ прямо сейчас. Назовите ЕЕ двумя словами.
+Ответ: Прыгающая лягушка.
+Зачёт: Скачущая лягушка.
+Комментарий: "Знаменитая скачущая лягушка из Калавераса" — первый опубликованный рассказ Марка Твена. В 1686 г. Басё сложил самое свое знаменитое стихотворение:
+    Старый пруд.
+    Прыгнула в воду лягушка.
+    Всплеск в тишине.
+    Принято считать, что этот звук пробудил Басё к истине Жизни по Дзен. "Прыгающая лягушка" — одна из фигур оригами. Лист бумаги (бланк для ответа) есть под рукой у каждой команды.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: Внимание, в вопросе есть замена.
+    В 1910 году один критик жаловался: "Третьего дня я провел несколько часов в сумасшедшем доме, причем среди буйно помешанных, — короче, был на "Пиковой даме"". Какие слова мы заменили словами "Пиковая дама"?
+Ответ: Бубновый валет.
+Комментарий: Имеется в виду знаменитая выставка русских авангардистов одноименного творческого объединения. Многим консервативно настроенным критикам их произведения казались чистым сумасшествием.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 19: По словам Ирины Вака́р, «ОН» в начале двадцатого века стал первой пощёчиной общественному вкусу. Раньше, по одной из версий, ОН изображался не с пикой, а с палитрой в руках. Назовите ЕГО.
+Ответ: «Бубновый валет»
+Зачёт: независимо от кавычек и капитализации.
+Комментарий: Речь о скандальной выставке 1910 года «Бубновый валет». По сомнительной версии Михаила Ларионова, бубновый валет эпохи Возрождения изображался с палитрой в руках. Пика, которой бубновый валет обзавёлся в XVIII веке, намекает на игральные карты.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 8: Написанная в 1913 году картина Ольги Розановой в буквальном переводе с английского снова на русский называется "Королева бриллиантов". Можно сказать, что женщина, изображенная на картине, немного старше Розановой и ее товарищей. Как эта картина называется по-русски?
+Ответ: "Бубновая дама".
+Зачёт: Дама бубен, дама бубей.
+Комментарий: По-английски Бубновая дама — Queen of diamonds. Ольга Розанова входила в группу художников "Бубновый валет". Бубновая дама старше бубнового валета.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 7
+Раздаточный материал
+https://gotquestions.online/pics/5913/399019_razdatka.png
+Существует легенда, что подобные дольме́ны были построены ПЕРВЫМИ для ВТОРЫХ. ПЕРВЫЕ и ВТОРЫЕ упоминаются в известном выражении. Напишите это выражение.
+Ответ: карлики на плечах у гигантов
+Зачёт: карлики на плечах великанов
+Комментарий: Кавказские дольмены – это грандиозные сооружения, а вот отверстия в них, обычно, крохотные, даже взрослому человеку не пролезть. Ученые считают, что дольмены служили своего рода фамильными склепами, а останки туда помещали через отверстия уже в скелетированном виде. Но у местных жителей была своя версия. Выражение, о котором идет речь, принадлежит, вероятнее всего, Бернáру Шáртрскому.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 8: Борис Пастернак, находясь в больнице, написал Андрею Вознесенскому письмо, в котором были такие строки: "Я всегда любил Вашу манеру видеть, думать, выражать себя. Но я не ждал, что ей удастся быть услышанной и признанной так скоро". Назовите двоих, которых упоминает Сергей Варшавчик, приводя этот факт.
+Ответ: [Гавриил Романович] Державин, [Александр Сергеевич] Пушкин.
+Комментарий: Тоже, в гроб сходя, благословил; это письмо было одним из последних писем Пастернака.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 4: Герой романа А.И. Куприна "Юнкера" Александров сокрушался: "Нет, но когда же я, черт побери, освоюсь с этой фортификационной путаницей, да будут прокляты и полковник Колосов, и его учитель Цезарь...". Закончите цитату одним словом.
+Ответ: Кюи.
+Комментарий: Композитор Ц.Я. Кюи (1835-1918) был военным инженером.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: Внимание, в вопросе есть замена.
+    Однажды в библиотеку к известному критику Стасову зашел генерал.
+    — Я опять к вам с просьбой, Владимир Васильевич, — сказал генерал.
+    — КУРФЮРСТ не просит, а повелевает, — отшутился Стасов.
+    Догадавшись, какое слово мы заменили словом "КУРФЮРСТ", назовите фамилию генерала.
+Ответ: Кюи.
+Комментарий: Курфюрст — Цезарь. Цезарь Антонович Кюи, известный композитор и член "Могучей кучки".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 30:
+Раздаточный материал
+    Мак
+    В этом вопросе ИКС заменяет два слова.
+    В книге «Тайный мир» Кристофер Эндрю объясняет неудачи русской армии в Первой мировой войне использованием ИКСА. Назовите уроженца Вильны, в фамилии которого на раздаточном материале мы заменили все буквы.
+Ответ: [Цезарь] Кюи.
+Зачёт: по фамилии «Кюи».
+Комментарий: в годы Первой мировой войны в российской армии все ещё пользовались шифром Цезаря — одним из самых простых способов кодирования информации. Немецким криптологам не составляло труда взломать такой шифр, что приводило к огромным потерям для царской России. Считается, что шифр Цезаря придумал Юлий Цезарь. Мы зашифровали фамилию композитора Цезаря Кюи, использовав алфавитный сдвиг вправо на две позиции.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 41:  Историки считают, что героями картины являются члены секты намдха̒ри, потерпевшие неудачу при захвате крепость Мало̒дх. А вот распространенное мнение ошибочное, ведь ОНО закончилось на 15 лет раньше. Назовите ЕГО.
+Ответ: Восстание сипа̒ев.
+Зачёт: Сипайское восстание; Индийское [народное] восстание;
+Комментарий: речь о картине «Подавление индийского восстания англичанами» Верещагина, на которой индийцев расстреливают из пушек. Верещагин, будучи в Индии в 1875 году, никак не мог видеть восстание сипаев, так как оно было подавлено 15 годами ранее. Но он застал там другие события: англичане казнили сектантов – участников бандитского нападения на несколько крепостей.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 7: В одном фантастическом фильме организм героини Мишель Родригез восстанавливается столь быстро, что пули, исторгнутые её телом, падают и ДЕЛАЮТ ЭТО. Герои романа «Колыбель для кошки» ДЕЛАЮТ ЭТО в последних главах. Что такое ДЕЛАТЬ ЭТО?
+Ответ: растапливать лёд
+Зачёт: растапливать снег, а также с любыми синонимами к слову «растапливать», например «плавить», «делать жидким», «превращать в воду».
+Комментарий: пули покидают тело за пару секунд, не успевая остыть. Как известно, ближе к концу романа Воннегута весь мир превращается в ледяную пустыню, и, желая выжить, герои растапливают лёд-9, чтобы получать питьевую воду.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 4: Тринадцатый и четырнадцатый открыты учеными в 2006 году и обладают, соответственно, моноклинной и орторомбической структурами кристаллических решеток. Назовите писателя, в романе которого роковую роль сыграл девятый.
+Ответ: Курт Воннегут.
+Зачёт: По фамилии.
+Комментарий: Речь идет о модификациях льда. Лед-9 вызвал катастрофу на Земле в книге Воннегута "Колыбель для кошки".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: 35 миллионов лет назад на месте леса ФонтенблО было море. Отступая, оно оставило слой уникального чистого песка. Именно поэтому лес ФонтенблО упоминается в статье про остров, находящийся примерно в тысяче километров к юго-востоку. Назовите этот остров.
+Ответ: МурАно.
+Комментарий: Венецианский остров МурАно славится своим стеклом. Один из секретов муранского стекла заключается в том, что для его производства используют чистейший в мире песок леса ФонтенблО.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 34: На одном острове особо чтят Святого Доната, который, после прихода варваров, восстановил церковный сосуд так хорошо, что ни одна капля не пролилась. Назовите этот остров несклоняемым словом.
+Ответ: Мурано.
+Зачёт: точный ответ.
+Комментарий: Святой Донат особо почитается на венецианском острове Мурано, который знаменит своими стеклянными изделиями. Донат смог восстановить разбитый варварами стеклянный потир.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 45: Этьен Жерар сообщает, что в 28 лет был полковником, а в 31 год – бригадиром. Далее Жерар говорит, что если бы война продлилась ещё два-три года, то наверняка получил бы ЕГО. Назовите ЕГО двумя словами.
+Ответ: Маршальский жезл
+Зачёт: Жезл маршала
+Комментарий: широко известен афоризм, приписываемый Наполеону: «Каждый солдат носит в ранце маршальский жезл». Жерар, конечно же, как солдат Великой армии тоже рассчитывал на него.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 2: Герой романа Вячеслава Сизова сделал в годы войны успешную карьеру. С собой он носил антикварный предмет, напоминающий ЕГО. Назовите ЕГО двумя словами.
+Ответ: маршальский жезл
+Комментарий: широко известен афоризм, приписываемый Наполеону: "Каждый солдат носит в ранце маршальский жезл", намекающий на мечту о военной карьере.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 5: Персонаж чешского писателя Милана Кундеры говорит об этом произведении, что оно "стоит костью в горле". Напишите название этого произведения, состоящее из пяти слов.
+Ответ: "Репортаж с петлей на шее".
+Комментарий: Произведение чешского журналиста Юлиуса Фучика. Горло и шея — это где-то рядом.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9:
+Раздаточный материал
+    Oh _____________
+    Your eyes are bright
+    And soft as dewy air.
+    Oh _____________
+    I am your knight
+    Although I have no spear.
+    Вы видите перед собой стихотворение Самуила Маршака, в котором мы сделали пропуски. Мы не стали его переводить. Кому оно посвящено?
+Ответ: Рита Райт-Ковалева.
+Комментарий: "Не стали переводить" — подсказка. Оба раза пропущено "Rita Wright"; Рита Райт-Ковалева — переводчица, коллега и знакомая Маршака. Да и рифмуется.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: По одной из версий, ОНА собирала слюну людей, умиравших под пыткой в застенках инквизиции. Назовите ЕЕ.
+Ответ: Тофана.
+Зачёт: Теофания ди Адамо.
+Комментарий: Было много разных гипотез по поводу рецепта ее знаменитого яда.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 14: Рассказывая о скульптуре Родена "Упавшая ОНА", один из комментаторов отметил, что тяжелая работа вовсе не для такого хрупкого создания. Назовите ЕЕ.
+Ответ: Кариатида.
+Комментарий: На скульптуре Родена кариатида упала под тяжестью камня.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 10: 
+Раздаточный материал
+    pass &lt;... ...&gt; through the gates of heaven
+    Перед вами фрагмент английского перевода эпитафии Анри Руссо. Ответьте, что впервые было открыто в Ирландии в 1947 году.
+Ответ: [Магазин] duty free.
+Комментарий: "Let our luggage pass duty free through the gates of heaven". Художник Анри Руссо, как известно, носил прозвище Таможенник.
+</t>
   </si>
 </sst>
 </file>
@@ -148,15 +649,21 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -185,21 +692,6 @@
       </left>
       <right style="medium">
         <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
@@ -241,21 +733,6 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
@@ -284,26 +761,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -320,29 +782,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -624,18 +1080,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,463 +1099,1078 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="133.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>45580</v>
+        <v>45683</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>45580</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="9">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="318" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="6">
+        <v>45683</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="278.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
-        <v>45580</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="9">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="6">
+        <v>45683</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
-        <v>45580</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="9">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="6">
+        <v>45683</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="10">
-        <v>45580</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="8">
+        <v>45683</v>
+      </c>
+      <c r="C6" s="10"/>
+    </row>
+    <row r="7" spans="1:3" ht="397.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
-        <v>45581</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="9">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="318" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="6">
+        <v>45684</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
-        <v>45581</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="9">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="6">
+        <v>45684</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
-        <v>45581</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="9">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="6">
+        <v>45684</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
-        <v>45581</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="9">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="6">
+        <v>45684</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="10">
-        <v>45581</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12" spans="1:4" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="8">
+        <v>45684</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="7">
-        <v>45582</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="9">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="6">
+        <v>45685</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="7">
-        <v>45582</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="9">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="6">
+        <v>45685</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
-        <v>45582</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="9">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="318" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="6">
+        <v>45685</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="304.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
-        <v>45582</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="9">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="6">
+        <v>45685</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="10">
-        <v>45582</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-    </row>
-    <row r="17" spans="1:4" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="8">
+        <v>45685</v>
+      </c>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
-        <v>45583</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="9">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="6">
+        <v>45686</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="7">
-        <v>45583</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="9">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="6">
+        <v>45686</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="291.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="7">
-        <v>45583</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="9">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="6">
+        <v>45686</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="7">
-        <v>45583</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="9">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="6">
+        <v>45686</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="10">
-        <v>45583</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="8">
+        <v>45686</v>
+      </c>
+      <c r="C21" s="10"/>
+    </row>
+    <row r="22" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="D22" s="9">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="6">
+        <v>45687</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="D23" s="9">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="6">
+        <v>45687</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="D24" s="9">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="6">
+        <v>45687</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="265.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="D25" s="9">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="6">
+        <v>45687</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="D26" s="13">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="8">
+        <v>45687</v>
+      </c>
+      <c r="C26" s="10"/>
+    </row>
+    <row r="27" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="D27" s="9">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="6">
+        <v>45688</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="D28" s="9">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6">
+        <v>45688</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="D29" s="9">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="6">
+        <v>45688</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="D30" s="9">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="6">
+        <v>45688</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="D31" s="12"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="8">
+        <v>45688</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="D32" s="9">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="6">
+        <v>45689</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="D33" s="9">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="6">
+        <v>45689</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="D34" s="9">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="6">
+        <v>45689</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="D35" s="9">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="6">
+        <v>45689</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="D36" s="12"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="8">
+        <v>45689</v>
+      </c>
+      <c r="C36" s="10"/>
+    </row>
+    <row r="37" spans="1:3" ht="265.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="D37" s="9">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="6">
+        <v>45690</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="D38" s="9">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="6">
+        <v>45690</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="D39" s="9">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="6">
+        <v>45690</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="D40" s="9">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="6">
+        <v>45690</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="D41" s="12"/>
-    </row>
-    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="8">
+        <v>45690</v>
+      </c>
+      <c r="C41" s="10"/>
+    </row>
+    <row r="42" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="D42" s="9">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="6">
+        <v>45691</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="D43" s="9">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="6">
+        <v>45691</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="278.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="D44" s="9">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="6">
+        <v>45691</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="D45" s="9">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="6">
+        <v>45691</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="D46" s="12"/>
+      <c r="B46" s="8">
+        <v>45691</v>
+      </c>
+      <c r="C46" s="10"/>
+    </row>
+    <row r="47" spans="1:3" ht="278.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6">
+        <v>45692</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" s="6">
+        <v>45692</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="304.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6">
+        <v>45692</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="397.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" s="6">
+        <v>45692</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8">
+        <v>45692</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" s="6">
+        <v>45693</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" s="6">
+        <v>45693</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" s="6">
+        <v>45693</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" s="6">
+        <v>45693</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" s="8">
+        <v>45693</v>
+      </c>
+      <c r="C56" s="10"/>
+    </row>
+    <row r="57" spans="1:3" ht="265.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" s="6">
+        <v>45694</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" s="6">
+        <v>45694</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" s="6">
+        <v>45694</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" s="6">
+        <v>45694</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8">
+        <v>45694</v>
+      </c>
+      <c r="C61" s="10"/>
+    </row>
+    <row r="62" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" s="6">
+        <v>45695</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" s="6">
+        <v>45695</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="397.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" s="6">
+        <v>45695</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="304.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" s="6">
+        <v>45695</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" s="8">
+        <v>45695</v>
+      </c>
+      <c r="C66" s="10"/>
+    </row>
+    <row r="67" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" s="6">
+        <v>45696</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" s="6">
+        <v>45696</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" s="6">
+        <v>45696</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" s="6">
+        <v>45696</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="304.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8">
+        <v>45696</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="291.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" s="6">
+        <v>45697</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="1">
+        <v>71</v>
+      </c>
+      <c r="B73" s="6">
+        <v>45697</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="1">
+        <v>72</v>
+      </c>
+      <c r="B74" s="6">
+        <v>45697</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="B75" s="6">
+        <v>45697</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="1">
+        <v>74</v>
+      </c>
+      <c r="B76" s="8">
+        <v>45697</v>
+      </c>
+      <c r="C76" s="10"/>
+    </row>
+    <row r="77" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="1">
+        <v>75</v>
+      </c>
+      <c r="B77" s="6">
+        <v>45698</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="278.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="B78" s="6">
+        <v>45698</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="1">
+        <v>77</v>
+      </c>
+      <c r="B79" s="6">
+        <v>45698</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="1">
+        <v>78</v>
+      </c>
+      <c r="B80" s="6">
+        <v>45698</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8">
+        <v>45698</v>
+      </c>
+      <c r="C81" s="10"/>
+    </row>
+    <row r="82" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="1">
+        <v>80</v>
+      </c>
+      <c r="B82" s="6">
+        <v>45699</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="1">
+        <v>81</v>
+      </c>
+      <c r="B83" s="6">
+        <v>45699</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="B84" s="6">
+        <v>45699</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="B85" s="6">
+        <v>45699</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="1">
+        <v>84</v>
+      </c>
+      <c r="B86" s="8">
+        <v>45699</v>
+      </c>
+      <c r="C86" s="10"/>
+    </row>
+    <row r="87" spans="1:3" ht="331.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="1">
+        <v>85</v>
+      </c>
+      <c r="B87" s="6">
+        <v>45700</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="B88" s="6">
+        <v>45700</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="120" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="1">
+        <v>87</v>
+      </c>
+      <c r="B89" s="6">
+        <v>45700</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="1">
+        <v>88</v>
+      </c>
+      <c r="B90" s="6">
+        <v>45700</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="1">
+        <v>89</v>
+      </c>
+      <c r="B91" s="8">
+        <v>45700</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="1">
+        <v>90</v>
+      </c>
+      <c r="B92" s="6">
+        <v>45701</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="1">
+        <v>91</v>
+      </c>
+      <c r="B93" s="6">
+        <v>45701</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="1">
+        <v>92</v>
+      </c>
+      <c r="B94" s="6">
+        <v>45701</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="1">
+        <v>93</v>
+      </c>
+      <c r="B95" s="6">
+        <v>45701</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="1">
+        <v>94</v>
+      </c>
+      <c r="B96" s="8">
+        <v>45701</v>
+      </c>
+      <c r="C96" s="10"/>
+    </row>
+    <row r="97" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="1">
+        <v>95</v>
+      </c>
+      <c r="B97" s="6">
+        <v>45702</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="397.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="1">
+        <v>96</v>
+      </c>
+      <c r="B98" s="6">
+        <v>45702</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="1">
+        <v>97</v>
+      </c>
+      <c r="B99" s="6">
+        <v>45702</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="1">
+        <v>98</v>
+      </c>
+      <c r="B100" s="6">
+        <v>45702</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="11">
+        <v>99</v>
+      </c>
+      <c r="B101" s="8">
+        <v>45702</v>
+      </c>
+      <c r="C101" s="10"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C104" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -27,142 +27,199 @@
     <t>Question</t>
   </si>
   <si>
-    <t xml:space="preserve">Вопрос 4: Согласно этимологическому словарю, слово "МУЗЫКА" родственно глаголу калмыцкого происхождения, означающему "взбивать воду", "рыхлить снег". Какое слово мы заменили словом "музыка"?
-Ответ: Сумбур.
-Комментарий: Вот такой "сумбур вместо музыки".
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 33: Ниро Вульф говорил, что готов к смертельной схватке с криминальным миром. Рекс СтАут отмечал, что на пейзаже в кабинете Вульфа изображён именно ОН. Назовите ЕГО двумя словами.
-Ответ: РейхенбАхский водопад.
-Комментарий: при необходимости Ниро Вульф готов дать смертельный бой криминальному миру, подобно тому как Шерлок Холмс рисковал жизнью, вступив в схватку с Мориарти на краю Рейхенбахского водопада. В самих книгах о Вульфе не сообщается, какой именно водопад изображён на картине, но в интервью Стаут уточнил, что по его задумке это именно Рейхенбахский водопад.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 268: Евгений Добренко пишет, что ОНА публиковалась в легко узнаваемых обложках салатного или кремового цветов. Назовите ЕЕ максимально точно.
-Ответ: "Книга о вкусной и здоровой пище".
-Комментарий: Цвета тоже "кулинарные".
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 11: Благодаря ЕЙ в 1970 году для Жванецкого и его коллег смягчили цензуру и отправили на гастроли по Украине для поднятия духа жителей страны. Как известно, ОНА благотворно сказалась и на творчестве другого литератора. Назовите ЕЕ максимально точно.
-Ответ: Холера.
-Зачёт: Эпидемия холеры.
-Комментарий: Благодаря карантину по поводу эпидемии холеры случилась Болдинская осень.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 3: В мультсериале "Симпсоны" местный пьяница, увидев страшного монстра, призывает на помощь старого знакомого, который растаптывает противника. Назовите этого знакомого.
-Ответ: Розовый слон.
-Комментарий: Страшный монстр был новой для пьяницы галлюцинацией. Испугавшись, он призвал более привычную.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 8: Написанная в 1913 году картина Ольги Розановой в буквальном переводе с английского снова на русский называется "Королева бриллиантов". Можно сказать, что женщина, изображенная на картине, немного старше Розановой и ее товарищей. Как эта картина называется по-русски?
-Ответ: "Бубновая дама".
-Зачёт: Дама бубен, дама бубей.
-Комментарий: По-английски Бубновая дама — Queen of diamonds. Ольга Розанова входила в группу художников "Бубновый валет". Бубновая дама старше бубнового валета.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 9: Внимание, в вопросе есть замена.
-    Однажды в библиотеку к известному критику Стасову зашел генерал.
-    — Я опять к вам с просьбой, Владимир Васильевич, — сказал генерал.
-    — КУРФЮРСТ не просит, а повелевает, — отшутился Стасов.
-    Догадавшись, какое слово мы заменили словом "КУРФЮРСТ", назовите фамилию генерала.
-Ответ: Кюи.
-Комментарий: Курфюрст — Цезарь. Цезарь Антонович Кюи, известный композитор и член "Могучей кучки".
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 30:
-Раздаточный материал
-    Мак
-    В этом вопросе ИКС заменяет два слова.
-    В книге «Тайный мир» Кристофер Эндрю объясняет неудачи русской армии в Первой мировой войне использованием ИКСА. Назовите уроженца Вильны, в фамилии которого на раздаточном материале мы заменили все буквы.
-Ответ: [Цезарь] Кюи.
-Зачёт: по фамилии «Кюи».
-Комментарий: в годы Первой мировой войны в российской армии все ещё пользовались шифром Цезаря — одним из самых простых способов кодирования информации. Немецким криптологам не составляло труда взломать такой шифр, что приводило к огромным потерям для царской России. Считается, что шифр Цезаря придумал Юлий Цезарь. Мы зашифровали фамилию композитора Цезаря Кюи, использовав алфавитный сдвиг вправо на две позиции.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 4: Тринадцатый и четырнадцатый открыты учеными в 2006 году и обладают, соответственно, моноклинной и орторомбической структурами кристаллических решеток. Назовите писателя, в романе которого роковую роль сыграл девятый.
-Ответ: Курт Воннегут.
+    <t>break</t>
+  </si>
+  <si>
+    <t>Лепорелло</t>
+  </si>
+  <si>
+    <t>венок сонетов</t>
+  </si>
+  <si>
+    <t>война токов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 12: В книге "Час быка" Иван Ефремов упоминает, что на столе у правителя-тирана Чойо Чагаса находилась символическая скульптура, изображающая ИХ. Мы не спрашиваем у вас, что делает или чего не делает каждая из НИХ. Назовите ИХ двумя словами.
+Ответ: Три обезьяны.
+Комментарий: Одна обезьяна заткнула уши, другая закрыла глаза, третья прикрыла рот — одна из обезьян ничего не слышит, вторая ничего не видит, третья ничего не говорит.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3:
+https://db.chgk.info/images/db/20120043.jpg
+    Назовите фамилию женщины, которая стоит справа от Курта Воннегута.
+Ответ: Райт-Ковалева.
+Зачёт: Рита Райт, Раиса Яковлевна Черномордик.
+Комментарий: Собственно известная переводчица писателя, слово "справа" — подсказка.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 1: Платон изображает ИХ сидящими на высоких стульях, в белых одеждах, с венками на головах: первая поет о настоящем, вторая — о прошедшем, третья — о будущем. Назовите имя любой из НИХ.
+Ответ: Клото, Лахесис, Атропос (Атропа).
+Зачёт: Любое из указанных имен.
+Комментарий: ОНИ — мойры; вопросом о вершительницах судьбы мы начали третий тур, который решит судьбу команд.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 10: 60-летний Мел Гибсон, объясняя, почему не ДЕЛАЕТ ЭТОГО, в шутку говорил, что в конце недели может сварить суп. Людям, которые также предпочитали не ДЕЛАТЬ ЭТОГО, обязан своим названием южноевропейский регион. Какие два слова, начинающиеся на одну и ту же букву, мы заменили словами "ДЕЛАТЬ ЭТО"?
+Ответ: Брить бороду.
+Комментарий: Гибсон шутит, что за неделю в бороде скапливаются остатки пищи, из которых можно приготовить суп. Название региона Ломбардия происходит от древнегерманского племени лангобардов (длиннобородых).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 13: Герой Германа Мелвилла — человек амбициозный, но пока не достигший больших успехов в жизни. Назовите двумя словами то, с чем Мелвилл сравнивает гарпун, который этот герой повсюду с собой носит.
+Ответ: Маршальский жезл.
+Комментарий: Всё в соответствии с наполеоновским высказыванием об амбициозном солдате, носящем в ранце маршальский жезл.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 7: Валерия Сирота обращает внимание, что этот человек проводил свои наблюдения, когда только что был завершен масштабный проект и готовился аналогичный другой. Назовите этого человека.
+Ответ: Джованни Скиапарелли
+Зачёт: по фамилии, с небольшими орфографическими ошибками
+Комментарий: был построен Суэцкий канал и обсуждалось строительство Панамского. Поэтому большие каналы были у всех на слуху и неудивительно, что Скиапарелли, увидев странные объекты на Марсе, тоже первым делом подумал про каналы.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 13: По одной из версий, у вынужденных переселенцев ОН стал аналогом проворной и сообразительной карликовой антилопы. Назовите ЕГО двумя словами.
+Ответ: Братец Кролик.
+Комментарий: Как и другие персонажи "Сказок дядюшки Римуса", хитроумный Братец Кролик является героем фольклора невольников-африканцев. Некоторые исследователи полагали, что в оригинальных африканских сказках роль трИкстера выполняла карликовая антилопа. Поскольку такое животное в Северной Америке не водилось, в фольклоре рабов трИкстером стал кролик.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 24: Оноре Домье оказался в тюрьме за то, что изобразил Луи-Филиппа в образе ОТЦА. А по замыслу автора, «ОТЕЦ и СЫН» – это сатира на церковь, белое духовенство и монашество. Ответьте, кого мы заменили на ОТЦА, или назовите того, кого мы заменили на СЫНА.
+Ответ: Гаргантюа.
+Зачёт: Пантагрюэль, с незначительными ошибками.
+Комментарий: Домье использовал образы, созданные его соотечественником Рабле. Франсуа Рабле, автор «Гаргантюа и Пантагрюэля», сам был монахом и в своей сатире высмеял церковь.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 29: Можно сказать, что название сборника, который состоит из пары романов и трёх рассказов Рекса Стаута, антонимично названию рассказа другого автора. Ответьте двумя английскими словами, как называется этот сборник.
+Ответ: Full House.
+Комментарий: этот сборник состоит из двух романов и трёх рассказов, поэтому название ему дала покерная комбинация фулл-хаус. В произведениях о Ниро Вульфе нередко встречаются отсылки к рассказам о Шерлоке Холмсе, а название этого сборника можно рассматривать как перевертыш названия рассказа «Пустой дом».
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: В детективном сериале "Касл" взрывается квартира вместе с одним из главных героев. Интересно, что развязка серии, в которой выясняется, что герой выжил, происходит в НЕМ. Назовите ЕГО двумя словами.
+Ответ: Пустой дом.
+Комментарий: "Пустой дом" — произведение Артура Конан Дойля, в котором становится известно, что Шерлок Холмс не погиб в водах Рейхенбахского водопада, как и герой сериала при взрыве.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 8: Через 15 лет после начала Холодной войны один американский сенатор в своей речи заявил: "Юрий Гагарин, русский герой, одновременно герой всего человечества. Мы должны заглушить в себе досаду и ревность". Однофамильцем какого изобретателя был этот сенатор?
+Ответ: [Роберт] Фултон.
+Комментарий: Точкой отсчета начала Холодной войны многие считают "Фултонскую речь" Черчилля, произнесенную в марте 1946 года. А эта "фултонская речь" (или, правильнее, "фултоновская"), по сути, наоборот, была против холодной войны. Американский инженер Роберт Фултон является создателем одного из первых пароходов и проекта одной из первых подводных лодок.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 69: 27 августа 1807 г. некий фермер из Олбани первым в мире заплатил шесть долларов за пользование изобретением, о котором много лет спустя спел Леонид Утесов. А кто получил эти шесть долларов за свое изобретение?
+Ответ: Роберт Фултон, изобретатель парохода.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9
+ В романе Александра Демидова из серии «Попаданец» в теле Гермионы Грейнджер оказывается одна из НИХ. Согласно аннотации, отныне Гарри Поттер не лучше всех владеет метлой, а аристократам фашистского толка наступит капут. Кто ОНИ?
+Ответ: фронтовые летчицы 46-го гвардейского бомбардировочного авиационного полка.
+Зачёт: «Ночные ведьмы»; по упоминанию Ночных ведьм.
+Комментарий: в романе «Товарищ Грейнджер» в Гермиону вселяется Ночная ведьма – одна из летчиц отечественного полка «Ночные ведьмы», которая охотится на фашистов и прекрасно владеет метлой.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 21
+ Многие модели самолетов времен Второй мировой войны имели особые прозвища. Например, Ла-5 [ла-пять] — "лавка", Пе-2 [пе-два] — "пешка", И-16 [и-шестнадцать] — "ишачок" и так далее. Автор вопроса придумал прозвище для самолетов По-2 [по-два], которыми был оснащен сорок шестой бомбардировочный авиационный полк. Напишите это прозвище.
+Ответ: Помело.
+Комментарий: Сорок шестой бомбардировочный авиационный полк — это знаменитые "Ночные ведьмы", полк, состоявший исключительно из женщин. Традиционно ведьма летает на помеле.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 14: В 1897 ОН писал брату: «Воздух, брат, отличный! Как в горах у нас в Сибири. &lt;…&gt;Туристов пропасть на каждом шагу». Назовите ЕГО.
+Ответ: [Василий Иванович] Суриков.
+Комментарий: красноярец писал из Швейцарии, куда приехал, чтобы написать этюды к картине «Переход Суворова через Альпы». Слово «пропасть» в вопросе – небольшая подсказка.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 6: Когда Франциск I пригласил Леонардо да Винчи к своему двору, Леонардо сделал это с несколькими своими картинами, включая "Мону Лизу". Назовите художника, который изобразил, как это делают русские.
+Ответ: Суриков.
+Комментарий: Леонардо перешел Альпы с рядом своих картин.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: Александр Горелов, говоря об этом писателе, замечает, что тот смог увидеть в российской провинции поистине шекспировские сюжеты. Назовите писателя, о котором идет речь.
+Ответ: Николай Семенович Лесков.
 Зачёт: По фамилии.
-Комментарий: Речь идет о модификациях льда. Лед-9 вызвал катастрофу на Земле в книге Воннегута "Колыбель для кошки".
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 34: На одном острове особо чтят Святого Доната, который, после прихода варваров, восстановил церковный сосуд так хорошо, что ни одна капля не пролилась. Назовите этот остров несклоняемым словом.
-Ответ: Мурано.
+Комментарий: Лесков — автор повести "Леди Макбет Мценского уезда".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9: Известный русский писатель вспоминал, как одному соседскому старику, "зажившемуся за семьдесят", нетерпеливая невестка влила в ухо кипящий сургуч. Какое произведение возникло под впечатлением от этого случая?
+Ответ: "Леди Макбет Мценского уезда".
+Комментарий: Похожим образом был убит отец Гамлета. Этот случай навел Н.С. Лескова на мысль о том, что и в русских селениях возможны шекспировские страсти.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 2: Критик писал о героине повести, что она — не луч солнца, падающий в темноту, а молния, порождённая самим мраком. Назовите фамилию этой героини.
+Ответ: Измайлова.
+Комментарий: Героиню повести Лескова "Леди Макбет Мценского уезда" Катерину Измайлову с её роковой тёмной страстью критики противопоставляли другой Катерине — героине пьесы "Гроза" Катерине Кабановой. Известная характеристика Катерины Кабановой — "луч света в тёмном царстве".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 18
+Раздаточный материал:
+The &lt;...&gt; isn't the &lt;...&gt;
+Когда у Стивена Гулда обнаружили рак, он выяснил что прогноз с таким видом рака — восемь месяцев. В своем эссе Гулд писал, что нужно уметь понимать статистику и призывал не отчаиваться: сам он прожил ещё двадцать лет после диагноза. В названии своего эссе Гулд обыгрывает известное выражение. Какие два слова, которые начинаются на одну и ту же букву, мы пропустили в этом названии?
+Ответ: median, message [ме́диан, ме́ссадж].
+Комментарий: медиана набора чисел — это число, которое находится в середине этого набора. В случае Гулда медианный прогноз продолжительности жизни с его видом рака был восемь месяцев. Название эссе отсылает к афоризму канадского культуролога Маршалла Маклюэна, который утверждал: «The medium is the message» [зе ме́диум из зе ме́ссадж].
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 9
+ Эксперимент показал, что дети, много смотревшие по телевизору образовательные передачи, впоследствии лучше учились и больше читали, чем те, которые смотрели по телевизору мультфильмы. Исследователи полагают, что эти результаты опровергают утверждение, сформулированное в шестидесятых годах. Назовите автора этого утверждения.
+Ответ: [Маршалл] Маклюэн.
+Комментарий: Исследователи хотели выяснить, что оказывает влияние на детей: сам факт того, что они смотрят телевизор, или какие именно передачи они смотрят. Оказалось, что существенно все-таки содержание, а не медиа, посредством которого это содержание доносилось до детей. Поэтому исследователи не согласны с высказыванием Маршалла МаклЮэна, и результаты работы резюмировали так: "The medium is not the message. The message is".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: В видеоклипе, стилизованном под ретро, певец стоит, облокотившись о ЕГО переднюю часть. Один коллекционер приобрел ЕГО за тысячу фунтов стерлингов. Назовите ЕГО точно.
+Ответ: Пенни-фартинг.
+Комментарий: Певец облокотился о переднее колесо высотой примерно в человеческий рост. Пенни-фартинги являются раритетными моделями велосипедов и стоят недешево.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 11: Сицилийское блюдо — крупные рисовые шарики, обжаренные в масле, — получило свое название в честь НИХ. В честь какой страны получили название сами ОНИ?
+Ответ: [в честь] Китая.
+Комментарий: аранчини по форме похожи на апельсины, которых много растет на Сицилии, а обжаренная корочка почти оранжевая. Слово «апельсин» во многих языках, в том числе в итальянском, происходит от слов «яблоко» и «китай».
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 6: В сказке Джанни Родари Апельсин просит Мандарина дать ему бутылку с желтой этикеткой, поскольку там, наверное, ТАКОЕ вино. Какое такое?
+Ответ: Китайское.
+Комментарий: Апельсин — китайское яблоко, Мандарин — китайский чиновник, да и этикетка желтая. :-)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 33: На похоронах герой Гюнтера Грасса хочет использовать гроб в качестве своего любимого предмета и взять в руки ИХ. Назовите ИХ двумя словами, начинающимися на парные согласные.
+Ответ: барабанные палочки.
 Зачёт: точный ответ.
-Комментарий: Святой Донат особо почитается на венецианском острове Мурано, который знаменит своими стеклянными изделиями. Донат смог восстановить разбитый варварами стеклянный потир.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 45: Этьен Жерар сообщает, что в 28 лет был полковником, а в 31 год – бригадиром. Далее Жерар говорит, что если бы война продлилась ещё два-три года, то наверняка получил бы ЕГО. Назовите ЕГО двумя словами.
-Ответ: Маршальский жезл
-Зачёт: Жезл маршала
-Комментарий: широко известен афоризм, приписываемый Наполеону: «Каждый солдат носит в ранце маршальский жезл». Жерар, конечно же, как солдат Великой армии тоже рассчитывал на него.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 2: Герой романа Вячеслава Сизова сделал в годы войны успешную карьеру. С собой он носил антикварный предмет, напоминающий ЕГО. Назовите ЕГО двумя словами.
-Ответ: маршальский жезл
-Комментарий: широко известен афоризм, приписываемый Наполеону: "Каждый солдат носит в ранце маршальский жезл", намекающий на мечту о военной карьере.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 5: Персонаж чешского писателя Милана Кундеры говорит об этом произведении, что оно "стоит костью в горле". Напишите название этого произведения, состоящее из пяти слов.
-Ответ: "Репортаж с петлей на шее".
-Комментарий: Произведение чешского журналиста Юлиуса Фучика. Горло и шея — это где-то рядом.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 9:
-Раздаточный материал
-    Oh _____________
-    Your eyes are bright
-    And soft as dewy air.
-    Oh _____________
-    I am your knight
-    Although I have no spear.
-    Вы видите перед собой стихотворение Самуила Маршака, в котором мы сделали пропуски. Мы не стали его переводить. Кому оно посвящено?
-Ответ: Рита Райт-Ковалева.
-Комментарий: "Не стали переводить" — подсказка. Оба раза пропущено "Rita Wright"; Рита Райт-Ковалева — переводчица, коллега и знакомая Маршака. Да и рифмуется.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 9: По одной из версий, ОНА собирала слюну людей, умиравших под пыткой в застенках инквизиции. Назовите ЕЕ.
-Ответ: Тофана.
-Зачёт: Теофания ди Адамо.
-Комментарий: Было много разных гипотез по поводу рецепта ее знаменитого яда.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 14: Рассказывая о скульптуре Родена "Упавшая ОНА", один из комментаторов отметил, что тяжелая работа вовсе не для такого хрупкого создания. Назовите ЕЕ.
-Ответ: Кариатида.
-Комментарий: На скульптуре Родена кариатида упала под тяжестью камня.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 10: 
-Раздаточный материал
-    pass &lt;... ...&gt; through the gates of heaven
-    Перед вами фрагмент английского перевода эпитафии Анри Руссо. Ответьте, что впервые было открыто в Ирландии в 1947 году.
-Ответ: [Магазин] duty free.
-Комментарий: "Let our luggage pass duty free through the gates of heaven". Художник Анри Руссо, как известно, носил прозвище Таможенник.
-</t>
-  </si>
-  <si>
-    <t>break</t>
+Комментарий: герой «Жестяного барабана» хочет на похоронах барабанить по крышке гроба палочками от своего барабана.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 10: Из его имени автор вопроса сделал вывод, что этот человек не спал, а покоился с миром. Назовите этого человека.
+Ответ: [Рип] Ван Винкль.
+Комментарий: Герой новеллы В. Ирвинга "Рип Ван Винкль" (1818), отведав напитка, погрузился в глубокий сон и проспал 20 лет; имя Rip соответствует аббревиатуре "R.I.P." — "requiescat in pace" (лат.), "rest in peace" (англ.) — "покойся с миром".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вопрос 3: В 1914 году известный политик, будучи уже немолодым, указывал на свою трость и грустно шутил: «Вот теперь моя ОНА!» Назовите ЕЁ двумя словами.
+Ответ: большая дубинка.
+Комментарий: речь о Теодоре Рузвельте, который прославился своей «политикой большой дубинки».
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +237,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -271,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -297,8 +361,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,18 +647,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="40.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.44140625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,621 +666,1240 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>45699</v>
+        <v>45719</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>45699</v>
+        <v>45719</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1">
+        <f>IF(ISTEXT(C3),MAX(E2,E1) + 1,"-")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>45699</v>
+        <v>45719</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="1">
+        <f t="shared" ref="E4:E67" si="0">IF(ISTEXT(C4),MAX(E3,E2) + 1,"-")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="4">
-        <v>45699</v>
+        <v>45719</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="6">
-        <v>45699</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="331.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>45719</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="4">
-        <v>45700</v>
+        <v>45720</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="265.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>45700</v>
+        <v>45720</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="120" thickBot="1" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="291.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>45700</v>
+        <v>45720</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="4">
-        <v>45700</v>
+        <v>45720</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="6">
-        <v>45700</v>
+        <v>45720</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="4">
-        <v>45701</v>
+        <v>45721</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="4">
-        <v>45701</v>
+        <v>45721</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="4">
-        <v>45701</v>
+        <v>45721</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="4">
-        <v>45701</v>
+        <v>45721</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="6">
-        <v>45701</v>
-      </c>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>45721</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="4">
-        <v>45702</v>
+        <v>45722</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="397.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="4">
-        <v>45702</v>
+        <v>45722</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="4">
-        <v>45702</v>
+        <v>45722</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="4">
-        <v>45702</v>
+        <v>45722</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="6">
-        <v>45702</v>
+        <v>45722</v>
       </c>
       <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="4">
+        <v>45723</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="4">
+        <v>45723</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="4">
+        <v>45723</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="4">
+        <v>45723</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="6">
+        <v>45723</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="4">
+        <v>45724</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="4">
+        <v>45724</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="4">
+        <v>45724</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="4">
+        <v>45724</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="6">
+        <v>45724</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" s="4">
+        <v>45725</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33" s="4">
+        <v>45725</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="133.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" s="4">
+        <v>45725</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35" s="4">
+        <v>45725</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" s="6">
+        <v>45725</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="E36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E66" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E67" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E68" s="1" t="str">
+        <f t="shared" ref="E68:E116" si="1">IF(ISTEXT(C68),MAX(E67,E66) + 1,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E69" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E70" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E71" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E72" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E73" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E74" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E75" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E76" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E77" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E78" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E79" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E80" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E81" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E82" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E83" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E84" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E85" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E86" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E87" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E88" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E89" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E90" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E91" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E92" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E93" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E94" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E95" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E96" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E97" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E98" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E99" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="9">
+      <c r="E100" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
         <v>99</v>
+      </c>
+      <c r="E101" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>100</v>
+      </c>
+      <c r="E102" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>101</v>
+      </c>
+      <c r="E103" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>102</v>
+      </c>
+      <c r="E104" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>103</v>
+      </c>
+      <c r="E105" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>104</v>
+      </c>
+      <c r="E106" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>105</v>
+      </c>
+      <c r="E107" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>106</v>
+      </c>
+      <c r="E108" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>107</v>
+      </c>
+      <c r="E109" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>108</v>
+      </c>
+      <c r="E110" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>109</v>
+      </c>
+      <c r="E111" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>110</v>
+      </c>
+      <c r="E112" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>111</v>
+      </c>
+      <c r="E113" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>112</v>
+      </c>
+      <c r="E114" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>113</v>
+      </c>
+      <c r="E115" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>114</v>
+      </c>
+      <c r="E116" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Date</t>
   </si>
@@ -27,56 +27,9 @@
     <t>Question</t>
   </si>
   <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>Лепорелло</t>
-  </si>
-  <si>
-    <t>венок сонетов</t>
-  </si>
-  <si>
-    <t>война токов</t>
-  </si>
-  <si>
     <t xml:space="preserve">Вопрос 12: В книге "Час быка" Иван Ефремов упоминает, что на столе у правителя-тирана Чойо Чагаса находилась символическая скульптура, изображающая ИХ. Мы не спрашиваем у вас, что делает или чего не делает каждая из НИХ. Назовите ИХ двумя словами.
 Ответ: Три обезьяны.
 Комментарий: Одна обезьяна заткнула уши, другая закрыла глаза, третья прикрыла рот — одна из обезьян ничего не слышит, вторая ничего не видит, третья ничего не говорит.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 3:
-https://db.chgk.info/images/db/20120043.jpg
-    Назовите фамилию женщины, которая стоит справа от Курта Воннегута.
-Ответ: Райт-Ковалева.
-Зачёт: Рита Райт, Раиса Яковлевна Черномордик.
-Комментарий: Собственно известная переводчица писателя, слово "справа" — подсказка.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 1: Платон изображает ИХ сидящими на высоких стульях, в белых одеждах, с венками на головах: первая поет о настоящем, вторая — о прошедшем, третья — о будущем. Назовите имя любой из НИХ.
-Ответ: Клото, Лахесис, Атропос (Атропа).
-Зачёт: Любое из указанных имен.
-Комментарий: ОНИ — мойры; вопросом о вершительницах судьбы мы начали третий тур, который решит судьбу команд.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 10: 60-летний Мел Гибсон, объясняя, почему не ДЕЛАЕТ ЭТОГО, в шутку говорил, что в конце недели может сварить суп. Людям, которые также предпочитали не ДЕЛАТЬ ЭТОГО, обязан своим названием южноевропейский регион. Какие два слова, начинающиеся на одну и ту же букву, мы заменили словами "ДЕЛАТЬ ЭТО"?
-Ответ: Брить бороду.
-Комментарий: Гибсон шутит, что за неделю в бороде скапливаются остатки пищи, из которых можно приготовить суп. Название региона Ломбардия происходит от древнегерманского племени лангобардов (длиннобородых).
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 13: Герой Германа Мелвилла — человек амбициозный, но пока не достигший больших успехов в жизни. Назовите двумя словами то, с чем Мелвилл сравнивает гарпун, который этот герой повсюду с собой носит.
-Ответ: Маршальский жезл.
-Комментарий: Всё в соответствии с наполеоновским высказыванием об амбициозном солдате, носящем в ранце маршальский жезл.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 7: Валерия Сирота обращает внимание, что этот человек проводил свои наблюдения, когда только что был завершен масштабный проект и готовился аналогичный другой. Назовите этого человека.
-Ответ: Джованни Скиапарелли
-Зачёт: по фамилии, с небольшими орфографическими ошибками
-Комментарий: был построен Суэцкий канал и обсуждалось строительство Панамского. Поэтому большие каналы были у всех на слуху и неудивительно, что Скиапарелли, увидев странные объекты на Марсе, тоже первым делом подумал про каналы.
 </t>
   </si>
   <si>
@@ -86,132 +39,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Вопрос 24: Оноре Домье оказался в тюрьме за то, что изобразил Луи-Филиппа в образе ОТЦА. А по замыслу автора, «ОТЕЦ и СЫН» – это сатира на церковь, белое духовенство и монашество. Ответьте, кого мы заменили на ОТЦА, или назовите того, кого мы заменили на СЫНА.
-Ответ: Гаргантюа.
-Зачёт: Пантагрюэль, с незначительными ошибками.
-Комментарий: Домье использовал образы, созданные его соотечественником Рабле. Франсуа Рабле, автор «Гаргантюа и Пантагрюэля», сам был монахом и в своей сатире высмеял церковь.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 29: Можно сказать, что название сборника, который состоит из пары романов и трёх рассказов Рекса Стаута, антонимично названию рассказа другого автора. Ответьте двумя английскими словами, как называется этот сборник.
-Ответ: Full House.
-Комментарий: этот сборник состоит из двух романов и трёх рассказов, поэтому название ему дала покерная комбинация фулл-хаус. В произведениях о Ниро Вульфе нередко встречаются отсылки к рассказам о Шерлоке Холмсе, а название этого сборника можно рассматривать как перевертыш названия рассказа «Пустой дом».
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 9: В детективном сериале "Касл" взрывается квартира вместе с одним из главных героев. Интересно, что развязка серии, в которой выясняется, что герой выжил, происходит в НЕМ. Назовите ЕГО двумя словами.
-Ответ: Пустой дом.
-Комментарий: "Пустой дом" — произведение Артура Конан Дойля, в котором становится известно, что Шерлок Холмс не погиб в водах Рейхенбахского водопада, как и герой сериала при взрыве.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 8: Через 15 лет после начала Холодной войны один американский сенатор в своей речи заявил: "Юрий Гагарин, русский герой, одновременно герой всего человечества. Мы должны заглушить в себе досаду и ревность". Однофамильцем какого изобретателя был этот сенатор?
-Ответ: [Роберт] Фултон.
-Комментарий: Точкой отсчета начала Холодной войны многие считают "Фултонскую речь" Черчилля, произнесенную в марте 1946 года. А эта "фултонская речь" (или, правильнее, "фултоновская"), по сути, наоборот, была против холодной войны. Американский инженер Роберт Фултон является создателем одного из первых пароходов и проекта одной из первых подводных лодок.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 69: 27 августа 1807 г. некий фермер из Олбани первым в мире заплатил шесть долларов за пользование изобретением, о котором много лет спустя спел Леонид Утесов. А кто получил эти шесть долларов за свое изобретение?
-Ответ: Роберт Фултон, изобретатель парохода.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 9
- В романе Александра Демидова из серии «Попаданец» в теле Гермионы Грейнджер оказывается одна из НИХ. Согласно аннотации, отныне Гарри Поттер не лучше всех владеет метлой, а аристократам фашистского толка наступит капут. Кто ОНИ?
-Ответ: фронтовые летчицы 46-го гвардейского бомбардировочного авиационного полка.
-Зачёт: «Ночные ведьмы»; по упоминанию Ночных ведьм.
-Комментарий: в романе «Товарищ Грейнджер» в Гермиону вселяется Ночная ведьма – одна из летчиц отечественного полка «Ночные ведьмы», которая охотится на фашистов и прекрасно владеет метлой.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 21
- Многие модели самолетов времен Второй мировой войны имели особые прозвища. Например, Ла-5 [ла-пять] — "лавка", Пе-2 [пе-два] — "пешка", И-16 [и-шестнадцать] — "ишачок" и так далее. Автор вопроса придумал прозвище для самолетов По-2 [по-два], которыми был оснащен сорок шестой бомбардировочный авиационный полк. Напишите это прозвище.
-Ответ: Помело.
-Комментарий: Сорок шестой бомбардировочный авиационный полк — это знаменитые "Ночные ведьмы", полк, состоявший исключительно из женщин. Традиционно ведьма летает на помеле.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 14: В 1897 ОН писал брату: «Воздух, брат, отличный! Как в горах у нас в Сибири. &lt;…&gt;Туристов пропасть на каждом шагу». Назовите ЕГО.
-Ответ: [Василий Иванович] Суриков.
-Комментарий: красноярец писал из Швейцарии, куда приехал, чтобы написать этюды к картине «Переход Суворова через Альпы». Слово «пропасть» в вопросе – небольшая подсказка.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 6: Когда Франциск I пригласил Леонардо да Винчи к своему двору, Леонардо сделал это с несколькими своими картинами, включая "Мону Лизу". Назовите художника, который изобразил, как это делают русские.
-Ответ: Суриков.
-Комментарий: Леонардо перешел Альпы с рядом своих картин.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 3: Александр Горелов, говоря об этом писателе, замечает, что тот смог увидеть в российской провинции поистине шекспировские сюжеты. Назовите писателя, о котором идет речь.
-Ответ: Николай Семенович Лесков.
-Зачёт: По фамилии.
-Комментарий: Лесков — автор повести "Леди Макбет Мценского уезда".
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Вопрос 9: Известный русский писатель вспоминал, как одному соседскому старику, "зажившемуся за семьдесят", нетерпеливая невестка влила в ухо кипящий сургуч. Какое произведение возникло под впечатлением от этого случая?
 Ответ: "Леди Макбет Мценского уезда".
 Комментарий: Похожим образом был убит отец Гамлета. Этот случай навел Н.С. Лескова на мысль о том, что и в русских селениях возможны шекспировские страсти.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 2: Критик писал о героине повести, что она — не луч солнца, падающий в темноту, а молния, порождённая самим мраком. Назовите фамилию этой героини.
-Ответ: Измайлова.
-Комментарий: Героиню повести Лескова "Леди Макбет Мценского уезда" Катерину Измайлову с её роковой тёмной страстью критики противопоставляли другой Катерине — героине пьесы "Гроза" Катерине Кабановой. Известная характеристика Катерины Кабановой — "луч света в тёмном царстве".
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 18
-Раздаточный материал:
-The &lt;...&gt; isn't the &lt;...&gt;
-Когда у Стивена Гулда обнаружили рак, он выяснил что прогноз с таким видом рака — восемь месяцев. В своем эссе Гулд писал, что нужно уметь понимать статистику и призывал не отчаиваться: сам он прожил ещё двадцать лет после диагноза. В названии своего эссе Гулд обыгрывает известное выражение. Какие два слова, которые начинаются на одну и ту же букву, мы пропустили в этом названии?
-Ответ: median, message [ме́диан, ме́ссадж].
-Комментарий: медиана набора чисел — это число, которое находится в середине этого набора. В случае Гулда медианный прогноз продолжительности жизни с его видом рака был восемь месяцев. Название эссе отсылает к афоризму канадского культуролога Маршалла Маклюэна, который утверждал: «The medium is the message» [зе ме́диум из зе ме́ссадж].
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 9
- Эксперимент показал, что дети, много смотревшие по телевизору образовательные передачи, впоследствии лучше учились и больше читали, чем те, которые смотрели по телевизору мультфильмы. Исследователи полагают, что эти результаты опровергают утверждение, сформулированное в шестидесятых годах. Назовите автора этого утверждения.
-Ответ: [Маршалл] Маклюэн.
-Комментарий: Исследователи хотели выяснить, что оказывает влияние на детей: сам факт того, что они смотрят телевизор, или какие именно передачи они смотрят. Оказалось, что существенно все-таки содержание, а не медиа, посредством которого это содержание доносилось до детей. Поэтому исследователи не согласны с высказыванием Маршалла МаклЮэна, и результаты работы резюмировали так: "The medium is not the message. The message is".
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 3: В видеоклипе, стилизованном под ретро, певец стоит, облокотившись о ЕГО переднюю часть. Один коллекционер приобрел ЕГО за тысячу фунтов стерлингов. Назовите ЕГО точно.
-Ответ: Пенни-фартинг.
-Комментарий: Певец облокотился о переднее колесо высотой примерно в человеческий рост. Пенни-фартинги являются раритетными моделями велосипедов и стоят недешево.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 11: Сицилийское блюдо — крупные рисовые шарики, обжаренные в масле, — получило свое название в честь НИХ. В честь какой страны получили название сами ОНИ?
-Ответ: [в честь] Китая.
-Комментарий: аранчини по форме похожи на апельсины, которых много растет на Сицилии, а обжаренная корочка почти оранжевая. Слово «апельсин» во многих языках, в том числе в итальянском, происходит от слов «яблоко» и «китай».
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 6: В сказке Джанни Родари Апельсин просит Мандарина дать ему бутылку с желтой этикеткой, поскольку там, наверное, ТАКОЕ вино. Какое такое?
-Ответ: Китайское.
-Комментарий: Апельсин — китайское яблоко, Мандарин — китайский чиновник, да и этикетка желтая. :-)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 33: На похоронах герой Гюнтера Грасса хочет использовать гроб в качестве своего любимого предмета и взять в руки ИХ. Назовите ИХ двумя словами, начинающимися на парные согласные.
-Ответ: барабанные палочки.
-Зачёт: точный ответ.
-Комментарий: герой «Жестяного барабана» хочет на похоронах барабанить по крышке гроба палочками от своего барабана.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 10: Из его имени автор вопроса сделал вывод, что этот человек не спал, а покоился с миром. Назовите этого человека.
-Ответ: [Рип] Ван Винкль.
-Комментарий: Герой новеллы В. Ирвинга "Рип Ван Винкль" (1818), отведав напитка, погрузился в глубокий сон и проспал 20 лет; имя Rip соответствует аббревиатуре "R.I.P." — "requiescat in pace" (лат.), "rest in peace" (англ.) — "покойся с миром".
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 3: В 1914 году известный политик, будучи уже немолодым, указывал на свою трость и грустно шутил: «Вот теперь моя ОНА!» Назовите ЕЁ двумя словами.
-Ответ: большая дубинка.
-Комментарий: речь о Теодоре Рузвельте, который прославился своей «политикой большой дубинки».
 </t>
   </si>
 </sst>
@@ -219,7 +49,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,29 +71,16 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -301,41 +118,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -351,21 +138,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,15 +438,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>45719</v>
+        <v>45722</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -685,500 +457,316 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>45719</v>
+        <v>45722</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1">
-        <f>IF(ISTEXT(C3),MAX(E2,E1) + 1,"-")</f>
+        <f ca="1">IF(ISTEXT(INDIRECT(ADDRESS(ROW(),3))),MAX(E2,E1) + 1,"-")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>45719</v>
+        <v>45722</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E67" si="0">IF(ISTEXT(C4),MAX(E3,E2) + 1,"-")</f>
+        <f t="shared" ref="E4:E67" ca="1" si="0">IF(ISTEXT(INDIRECT(ADDRESS(ROW(),3))),MAX(E3,E2) + 1,"-")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
-        <v>45719</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="6">
-        <v>45719</v>
-      </c>
-      <c r="C6" s="8"/>
       <c r="E6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
-        <v>45720</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="265.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E7" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
-        <v>45720</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="291.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
-        <v>45720</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
-        <v>45720</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="6">
-        <v>45720</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
-        <v>45721</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="172.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="4">
-        <v>45721</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="4">
-        <v>45721</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="4">
-        <v>45721</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="6">
-        <v>45721</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="4">
-        <v>45722</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="4">
-        <v>45722</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E18" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="4">
-        <v>45722</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="186" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="4">
-        <v>45722</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="6">
-        <v>45722</v>
-      </c>
-      <c r="C21" s="8"/>
       <c r="E21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="4">
-        <v>45723</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E22" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="4">
-        <v>45723</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="4">
-        <v>45723</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E24" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="4">
-        <v>45723</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="1">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="6">
-        <v>45723</v>
-      </c>
-      <c r="C26" s="10"/>
       <c r="E26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="4">
-        <v>45724</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="1">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="146.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E27" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="4">
-        <v>45724</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="159.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="4">
-        <v>45724</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E29" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="4">
-        <v>45724</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="6">
-        <v>45724</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E31" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="4">
-        <v>45725</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="4">
-        <v>45725</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="1">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="133.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E33" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="4">
-        <v>45725</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E34" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="4">
-        <v>45725</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="1">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="6">
-        <v>45725</v>
-      </c>
-      <c r="C36" s="8"/>
       <c r="E36" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1187,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="E37" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1196,7 +784,7 @@
         <v>36</v>
       </c>
       <c r="E38" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1205,7 +793,7 @@
         <v>37</v>
       </c>
       <c r="E39" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1214,7 +802,7 @@
         <v>38</v>
       </c>
       <c r="E40" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1223,7 +811,7 @@
         <v>39</v>
       </c>
       <c r="E41" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1232,7 +820,7 @@
         <v>40</v>
       </c>
       <c r="E42" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1241,7 +829,7 @@
         <v>41</v>
       </c>
       <c r="E43" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1250,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="E44" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1259,7 +847,7 @@
         <v>43</v>
       </c>
       <c r="E45" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1268,7 +856,7 @@
         <v>44</v>
       </c>
       <c r="E46" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1277,7 +865,7 @@
         <v>45</v>
       </c>
       <c r="E47" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1286,7 +874,7 @@
         <v>46</v>
       </c>
       <c r="E48" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1295,7 +883,7 @@
         <v>47</v>
       </c>
       <c r="E49" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1304,7 +892,7 @@
         <v>48</v>
       </c>
       <c r="E50" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1313,7 +901,7 @@
         <v>49</v>
       </c>
       <c r="E51" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1322,7 +910,7 @@
         <v>50</v>
       </c>
       <c r="E52" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1331,7 +919,7 @@
         <v>51</v>
       </c>
       <c r="E53" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1340,7 +928,7 @@
         <v>52</v>
       </c>
       <c r="E54" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1349,7 +937,7 @@
         <v>53</v>
       </c>
       <c r="E55" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1358,7 +946,7 @@
         <v>54</v>
       </c>
       <c r="E56" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1367,7 +955,7 @@
         <v>55</v>
       </c>
       <c r="E57" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1376,7 +964,7 @@
         <v>56</v>
       </c>
       <c r="E58" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1385,7 +973,7 @@
         <v>57</v>
       </c>
       <c r="E59" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1394,7 +982,7 @@
         <v>58</v>
       </c>
       <c r="E60" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1403,7 +991,7 @@
         <v>59</v>
       </c>
       <c r="E61" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1412,7 +1000,7 @@
         <v>60</v>
       </c>
       <c r="E62" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1421,7 +1009,7 @@
         <v>61</v>
       </c>
       <c r="E63" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1430,7 +1018,7 @@
         <v>62</v>
       </c>
       <c r="E64" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1439,7 +1027,7 @@
         <v>63</v>
       </c>
       <c r="E65" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1448,7 +1036,7 @@
         <v>64</v>
       </c>
       <c r="E66" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1457,7 +1045,7 @@
         <v>65</v>
       </c>
       <c r="E67" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>-</v>
       </c>
     </row>
@@ -1466,7 +1054,7 @@
         <v>66</v>
       </c>
       <c r="E68" s="1" t="str">
-        <f t="shared" ref="E68:E116" si="1">IF(ISTEXT(C68),MAX(E67,E66) + 1,"-")</f>
+        <f t="shared" ref="E68:E116" ca="1" si="1">IF(ISTEXT(INDIRECT(ADDRESS(ROW(),3))),MAX(E67,E66) + 1,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -1475,7 +1063,7 @@
         <v>67</v>
       </c>
       <c r="E69" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1484,7 +1072,7 @@
         <v>68</v>
       </c>
       <c r="E70" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1493,7 +1081,7 @@
         <v>69</v>
       </c>
       <c r="E71" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1502,7 +1090,7 @@
         <v>70</v>
       </c>
       <c r="E72" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1511,7 +1099,7 @@
         <v>71</v>
       </c>
       <c r="E73" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1520,7 +1108,7 @@
         <v>72</v>
       </c>
       <c r="E74" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1529,7 +1117,7 @@
         <v>73</v>
       </c>
       <c r="E75" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1538,7 +1126,7 @@
         <v>74</v>
       </c>
       <c r="E76" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1547,7 +1135,7 @@
         <v>75</v>
       </c>
       <c r="E77" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1556,7 +1144,7 @@
         <v>76</v>
       </c>
       <c r="E78" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1565,7 +1153,7 @@
         <v>77</v>
       </c>
       <c r="E79" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1574,7 +1162,7 @@
         <v>78</v>
       </c>
       <c r="E80" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1583,7 +1171,7 @@
         <v>79</v>
       </c>
       <c r="E81" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1592,7 +1180,7 @@
         <v>80</v>
       </c>
       <c r="E82" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1601,7 +1189,7 @@
         <v>81</v>
       </c>
       <c r="E83" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1610,7 +1198,7 @@
         <v>82</v>
       </c>
       <c r="E84" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1619,7 +1207,7 @@
         <v>83</v>
       </c>
       <c r="E85" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1628,7 +1216,7 @@
         <v>84</v>
       </c>
       <c r="E86" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1637,7 +1225,7 @@
         <v>85</v>
       </c>
       <c r="E87" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1646,7 +1234,7 @@
         <v>86</v>
       </c>
       <c r="E88" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1655,7 +1243,7 @@
         <v>87</v>
       </c>
       <c r="E89" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1664,7 +1252,7 @@
         <v>88</v>
       </c>
       <c r="E90" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1673,7 +1261,7 @@
         <v>89</v>
       </c>
       <c r="E91" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1682,7 +1270,7 @@
         <v>90</v>
       </c>
       <c r="E92" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1691,7 +1279,7 @@
         <v>91</v>
       </c>
       <c r="E93" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1700,7 +1288,7 @@
         <v>92</v>
       </c>
       <c r="E94" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1709,7 +1297,7 @@
         <v>93</v>
       </c>
       <c r="E95" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1718,7 +1306,7 @@
         <v>94</v>
       </c>
       <c r="E96" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1727,7 +1315,7 @@
         <v>95</v>
       </c>
       <c r="E97" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1736,7 +1324,7 @@
         <v>96</v>
       </c>
       <c r="E98" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1745,7 +1333,7 @@
         <v>97</v>
       </c>
       <c r="E99" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1754,7 +1342,7 @@
         <v>98</v>
       </c>
       <c r="E100" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1763,7 +1351,7 @@
         <v>99</v>
       </c>
       <c r="E101" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1772,7 +1360,7 @@
         <v>100</v>
       </c>
       <c r="E102" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1781,7 +1369,7 @@
         <v>101</v>
       </c>
       <c r="E103" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1790,7 +1378,7 @@
         <v>102</v>
       </c>
       <c r="E104" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1799,7 +1387,7 @@
         <v>103</v>
       </c>
       <c r="E105" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1808,7 +1396,7 @@
         <v>104</v>
       </c>
       <c r="E106" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1817,7 +1405,7 @@
         <v>105</v>
       </c>
       <c r="E107" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1826,7 +1414,7 @@
         <v>106</v>
       </c>
       <c r="E108" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1835,7 +1423,7 @@
         <v>107</v>
       </c>
       <c r="E109" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1844,7 +1432,7 @@
         <v>108</v>
       </c>
       <c r="E110" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1853,7 +1441,7 @@
         <v>109</v>
       </c>
       <c r="E111" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1862,7 +1450,7 @@
         <v>110</v>
       </c>
       <c r="E112" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1871,7 +1459,7 @@
         <v>111</v>
       </c>
       <c r="E113" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1880,7 +1468,7 @@
         <v>112</v>
       </c>
       <c r="E114" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1889,7 +1477,7 @@
         <v>113</v>
       </c>
       <c r="E115" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>
@@ -1898,7 +1486,7 @@
         <v>114</v>
       </c>
       <c r="E116" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-</v>
       </c>
     </row>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -19,57 +19,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Date</t>
   </si>
   <si>
     <t>Question</t>
   </si>
-  <si>
-    <t xml:space="preserve">Вопрос 12: В книге "Час быка" Иван Ефремов упоминает, что на столе у правителя-тирана Чойо Чагаса находилась символическая скульптура, изображающая ИХ. Мы не спрашиваем у вас, что делает или чего не делает каждая из НИХ. Назовите ИХ двумя словами.
-Ответ: Три обезьяны.
-Комментарий: Одна обезьяна заткнула уши, другая закрыла глаза, третья прикрыла рот — одна из обезьян ничего не слышит, вторая ничего не видит, третья ничего не говорит.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 13: По одной из версий, у вынужденных переселенцев ОН стал аналогом проворной и сообразительной карликовой антилопы. Назовите ЕГО двумя словами.
-Ответ: Братец Кролик.
-Комментарий: Как и другие персонажи "Сказок дядюшки Римуса", хитроумный Братец Кролик является героем фольклора невольников-африканцев. Некоторые исследователи полагали, что в оригинальных африканских сказках роль трИкстера выполняла карликовая антилопа. Поскольку такое животное в Северной Америке не водилось, в фольклоре рабов трИкстером стал кролик.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вопрос 9: Известный русский писатель вспоминал, как одному соседскому старику, "зажившемуся за семьдесят", нетерпеливая невестка влила в ухо кипящий сургуч. Какое произведение возникло под впечатлением от этого случая?
-Ответ: "Леди Макбет Мценского уезда".
-Комментарий: Похожим образом был убит отец Гамлета. Этот случай навел Н.С. Лескова на мысль о том, что и в русских селениях возможны шекспировские страсти.
-</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -80,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -88,41 +56,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -133,17 +71,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -430,7 +373,7 @@
     <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,48 +381,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="199.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
-        <v>45722</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="252" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
-        <v>45722</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="E3" s="1" t="str">
         <f ca="1">IF(ISTEXT(INDIRECT(ADDRESS(ROW(),3))),MAX(E2,E1) + 1,"-")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="212.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>45722</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="E4" s="1" t="str">
         <f t="shared" ref="E4:E67" ca="1" si="0">IF(ISTEXT(INDIRECT(ADDRESS(ROW(),3))),MAX(E3,E2) + 1,"-")</f>
-        <v>3</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1491,6 +1416,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="break">
+      <formula>NOT(ISERROR(SEARCH("break",C1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
